--- a/quiz/수업도우미_퀴즈_문항과출처.xlsx
+++ b/quiz/수업도우미_퀴즈_문항과출처.xlsx
@@ -4501,7 +4501,7 @@
       </c>
       <c r="B95" s="7" t="inlineStr">
         <is>
-          <t>벽지나 부직포로 만든 종이 같은 물건은 종이류로 재활용된다.</t>
+          <t>사용한 화장지나 종이호일도 종이류로 재활용할 수 있다.</t>
         </is>
       </c>
       <c r="C95" s="6" t="inlineStr">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="D95" s="7" t="inlineStr">
         <is>
-          <t>틀려요! 벽지와 부직포는 종이로 재활용되지 않아요.</t>
+          <t>틀려요! 화장지와 종이호일은 종이류로 재활용되지 않아요.</t>
         </is>
       </c>
       <c r="E95" s="7" t="inlineStr">
@@ -4901,7 +4901,7 @@
       </c>
       <c r="B105" s="7" t="inlineStr">
         <is>
-          <t>거울이나 유리컵은 유리병 수거함에 넣으면 안 된다.</t>
+          <t>창문 유리나 사기그릇은 유리병 수거함에 넣으면 안 된다.</t>
         </is>
       </c>
       <c r="C105" s="6" t="inlineStr">
@@ -4911,7 +4911,7 @@
       </c>
       <c r="D105" s="7" t="inlineStr">
         <is>
-          <t>맞아요! 유리병과 성분이 달라 함께 넣으면 재활용을 방해해요.</t>
+          <t>맞아요! 판유리와 사기·도자기류는 유리병으로 재활용되지 않아요.</t>
         </is>
       </c>
       <c r="E105" s="7" t="inlineStr">
@@ -5021,7 +5021,7 @@
       </c>
       <c r="B108" s="14" t="inlineStr">
         <is>
-          <t>부탄가스 통은 남은 가스를 모두 쓴 뒤 구멍을 뚫어 배출한다.</t>
+          <t>부탄가스 통은 바람이 잘 통하는 곳에서 노즐을 눌러 남은 가스를 뺀 뒤 배출한다.</t>
         </is>
       </c>
       <c r="C108" s="13" t="inlineStr">
@@ -5031,7 +5031,7 @@
       </c>
       <c r="D108" s="14" t="inlineStr">
         <is>
-          <t>맞아요! 가스를 다 비우고 구멍을 내야 안전하게 재활용할 수 있어요.</t>
+          <t>맞아요! 구멍을 뚫지 말고 노즐을 눌러 가스를 빼야 안전해요.</t>
         </is>
       </c>
       <c r="E108" s="14" t="inlineStr">
@@ -10585,7 +10585,7 @@
       </c>
       <c r="D90" s="14" t="inlineStr">
         <is>
-          <t>맞아요! 손을 들면 운전자가 나를 더 잘 볼 수 있어요.</t>
+          <t>맞아요! 횡단보도 5원칙 가운데 하나가 «손을 들기» 예요.</t>
         </is>
       </c>
       <c r="E90" s="14" t="inlineStr">
@@ -10595,17 +10595,17 @@
       </c>
       <c r="F90" s="14" t="inlineStr">
         <is>
-          <t>행정안전부</t>
+          <t>대한민국 정책브리핑(문화체육관광부 운영)</t>
         </is>
       </c>
       <c r="G90" s="14" t="inlineStr">
         <is>
-          <t>어린이 안전 배움터 - 도로·교통(어린이보호구역 교통안전수칙)</t>
+          <t>새 학기, 자녀와 함께 교통안전수칙 알아봤습니다! (횡단보도 5원칙)</t>
         </is>
       </c>
       <c r="H90" s="15" t="inlineStr">
         <is>
-          <t>https://www.mois.go.kr/chd/sub/a06/road/screen.do</t>
+          <t>https://www.korea.kr/news/policyNewsView.do?newsId=148926855</t>
         </is>
       </c>
     </row>
@@ -10615,7 +10615,7 @@
       </c>
       <c r="B91" s="7" t="inlineStr">
         <is>
-          <t>초록불이 깜빡이기 시작하면 얼른 뛰어서 건너는 것이 좋아요.</t>
+          <t>초록불이면 차가 멈췄는지 보지 않고 바로 건너도 돼요.</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
@@ -10625,7 +10625,7 @@
       </c>
       <c r="D91" s="7" t="inlineStr">
         <is>
-          <t>틀려요! 깜빡이면 건너지 말고 다음 신호를 기다려요.</t>
+          <t>틀려요! 차가 완전히 멈춘 것을 확인한 뒤에 건너야 해요.</t>
         </is>
       </c>
       <c r="E91" s="7" t="inlineStr">
@@ -10635,17 +10635,17 @@
       </c>
       <c r="F91" s="7" t="inlineStr">
         <is>
-          <t>행정안전부</t>
+          <t>대한민국 정책브리핑(문화체육관광부 운영)</t>
         </is>
       </c>
       <c r="G91" s="7" t="inlineStr">
         <is>
-          <t>어린이 안전 배움터 - 도로·교통(어린이보호구역 교통안전수칙)</t>
+          <t>새 학기, 자녀와 함께 교통안전수칙 알아봤습니다! (횡단보도 5원칙)</t>
         </is>
       </c>
       <c r="H91" s="12" t="inlineStr">
         <is>
-          <t>https://www.mois.go.kr/chd/sub/a06/road/screen.do</t>
+          <t>https://www.korea.kr/news/policyNewsView.do?newsId=148926855</t>
         </is>
       </c>
     </row>
@@ -10665,7 +10665,7 @@
       </c>
       <c r="D92" s="14" t="inlineStr">
         <is>
-          <t>아니요! 도로에 뛰어들면 매우 위험하니 어른에게 부탁해요.</t>
+          <t>아니요! 도로로 뛰어들지 않는 것이 안전수칙이에요. 어른에게 부탁해요.</t>
         </is>
       </c>
       <c r="E92" s="14" t="inlineStr">
@@ -10675,17 +10675,17 @@
       </c>
       <c r="F92" s="14" t="inlineStr">
         <is>
-          <t>행정안전부</t>
+          <t>대한민국 정책브리핑(문화체육관광부 운영)</t>
         </is>
       </c>
       <c r="G92" s="14" t="inlineStr">
         <is>
-          <t>어린이 안전 배움터 - 도로·교통(어린이보호구역 교통안전수칙)</t>
+          <t>어린이 교통안전 수칙을 지켜라</t>
         </is>
       </c>
       <c r="H92" s="15" t="inlineStr">
         <is>
-          <t>https://www.mois.go.kr/chd/sub/a06/road/screen.do</t>
+          <t>https://www.korea.kr/news/policyNewsView.do?newsId=148954485</t>
         </is>
       </c>
     </row>
@@ -10735,7 +10735,7 @@
       </c>
       <c r="B94" s="14" t="inlineStr">
         <is>
-          <t>멈춰 서 있는 버스나 트럭 바로 앞뒤로 지나가면 위험해요.</t>
+          <t>횡단보도를 건널 때는 멈추기·좌우 살피기·손들기·차 멈춤 확인·건너기 순서를 지켜요.</t>
         </is>
       </c>
       <c r="C94" s="13" t="inlineStr">
@@ -10745,7 +10745,7 @@
       </c>
       <c r="D94" s="14" t="inlineStr">
         <is>
-          <t>맞아요! 큰 차 앞뒤는 운전자에게 보이지 않는 곳이라 위험해요.</t>
+          <t>맞아요! 이 다섯 가지가 횡단보도를 건너는 순서예요.</t>
         </is>
       </c>
       <c r="E94" s="14" t="inlineStr">
@@ -10755,17 +10755,17 @@
       </c>
       <c r="F94" s="14" t="inlineStr">
         <is>
-          <t>행정안전부</t>
+          <t>대한민국 정책브리핑(문화체육관광부 운영)</t>
         </is>
       </c>
       <c r="G94" s="14" t="inlineStr">
         <is>
-          <t>어린이 안전 배움터 - 도로·교통(어린이보호구역 교통안전수칙)</t>
+          <t>새 학기, 자녀와 함께 교통안전수칙 알아봤습니다! (횡단보도 5원칙)</t>
         </is>
       </c>
       <c r="H94" s="15" t="inlineStr">
         <is>
-          <t>https://www.mois.go.kr/chd/sub/a06/road/screen.do</t>
+          <t>https://www.korea.kr/news/policyNewsView.do?newsId=148926855</t>
         </is>
       </c>
     </row>
@@ -28184,7 +28184,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E94"/>
+  <dimension ref="A1:E96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -28249,11 +28249,11 @@
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>행정안전부</t>
+          <t>기후에너지환경부</t>
         </is>
       </c>
       <c r="B7" s="13" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C7" s="17">
         <f>B7/$B$22</f>
@@ -28263,11 +28263,11 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>기후에너지환경부</t>
+          <t>행정안전부</t>
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C8" s="16">
         <f>B8/$B$22</f>
@@ -28295,7 +28295,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C10" s="16">
         <f>B10/$B$22</f>
@@ -28474,7 +28474,7 @@
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t>문서별 (69종)</t>
+          <t>문서별 (71종)</t>
         </is>
       </c>
     </row>
@@ -28713,7 +28713,7 @@
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>어린이 안전 배움터 - 도로·교통(어린이보호구역 교통안전수칙)</t>
+          <t>국민안전24(옛 국민재난안전포털) - 지진 발생 시 국민행동요령</t>
         </is>
       </c>
       <c r="C34" s="6" t="n">
@@ -28726,23 +28726,23 @@
       </c>
       <c r="E34" s="12" t="inlineStr">
         <is>
-          <t>https://www.mois.go.kr/chd/sub/a06/road/screen.do</t>
+          <t>https://www.safekorea.go.kr/safekorea-kor/em/emergency/emergency_eq2.html</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="14" t="inlineStr">
         <is>
-          <t>행정안전부</t>
+          <t>법제처(찾기쉬운 생활법령정보)</t>
         </is>
       </c>
       <c r="B35" s="14" t="inlineStr">
         <is>
-          <t>국민안전24(옛 국민재난안전포털) - 지진 발생 시 국민행동요령</t>
+          <t>찾기쉬운 생활법령정보 - 화재예방을 위한 안전수칙</t>
         </is>
       </c>
       <c r="C35" s="13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D35" s="14" t="inlineStr">
         <is>
@@ -28751,19 +28751,19 @@
       </c>
       <c r="E35" s="15" t="inlineStr">
         <is>
-          <t>https://www.safekorea.go.kr/safekorea-kor/em/emergency/emergency_eq2.html</t>
+          <t>https://easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=690&amp;ccfNo=5&amp;cciNo=1&amp;cnpClsNo=1</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>법제처(찾기쉬운 생활법령정보)</t>
+          <t>식품의약품안전처</t>
         </is>
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>찾기쉬운 생활법령정보 - 화재예방을 위한 안전수칙</t>
+          <t>서울지방식품의약품안전청 - 식중독 예방 6대 요령</t>
         </is>
       </c>
       <c r="C36" s="6" t="n">
@@ -28776,69 +28776,69 @@
       </c>
       <c r="E36" s="12" t="inlineStr">
         <is>
-          <t>https://easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=690&amp;ccfNo=5&amp;cciNo=1&amp;cnpClsNo=1</t>
+          <t>https://www.mfds.go.kr/brd/m_827/view.do?seq=3609</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="14" t="inlineStr">
         <is>
-          <t>식품의약품안전처</t>
+          <t>대한민국 정책브리핑(문화체육관광부 운영)</t>
         </is>
       </c>
       <c r="B37" s="14" t="inlineStr">
         <is>
-          <t>서울지방식품의약품안전청 - 식중독 예방 6대 요령</t>
+          <t>올바른 분리배출의 기준, 네 가지</t>
         </is>
       </c>
       <c r="C37" s="13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D37" s="14" t="inlineStr">
         <is>
-          <t>안전</t>
+          <t>환경</t>
         </is>
       </c>
       <c r="E37" s="15" t="inlineStr">
         <is>
-          <t>https://www.mfds.go.kr/brd/m_827/view.do?seq=3609</t>
+          <t>https://www.korea.kr/news/policyNewsView.do?newsId=148942053</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>대한민국 정책브리핑(문화체육관광부 운영)</t>
+          <t>교육부</t>
         </is>
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>올바른 분리배출의 기준, 네 가지</t>
+          <t>2025년 1차 학교폭력 실태조사(전수조사) 주요 결과표</t>
         </is>
       </c>
       <c r="C38" s="6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>환경</t>
+          <t>학교폭력</t>
         </is>
       </c>
       <c r="E38" s="12" t="inlineStr">
         <is>
-          <t>https://www.korea.kr/news/policyNewsView.do?newsId=148942053</t>
+          <t>https://www.goe.go.kr/resource/goe/na/bbs_2675/2026/01/4e4fd915-99e8-43d0-b763-3b0bfea0b50b.pdf</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="14" t="inlineStr">
         <is>
-          <t>교육부</t>
+          <t>대한심폐소생협회</t>
         </is>
       </c>
       <c r="B39" s="14" t="inlineStr">
         <is>
-          <t>2025년 1차 학교폭력 실태조사(전수조사) 주요 결과표</t>
+          <t>심폐소생술 시행방법</t>
         </is>
       </c>
       <c r="C39" s="13" t="n">
@@ -28846,24 +28846,24 @@
       </c>
       <c r="D39" s="14" t="inlineStr">
         <is>
-          <t>학교폭력</t>
+          <t>안전</t>
         </is>
       </c>
       <c r="E39" s="15" t="inlineStr">
         <is>
-          <t>https://www.goe.go.kr/resource/goe/na/bbs_2675/2026/01/4e4fd915-99e8-43d0-b763-3b0bfea0b50b.pdf</t>
+          <t>https://www.kacpr.org/page/page.php?category_idx=3&amp;category1_code=1247206302&amp;category2_code=1527742406&amp;page_idx=1118</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>대한심폐소생협회</t>
+          <t>법제처(찾기쉬운 생활법령정보)</t>
         </is>
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>심폐소생술 시행방법</t>
+          <t>학교폭력 &gt; 학교폭력의 이해 &gt; 학교폭력의 개념 (학교폭력예방 및 대책에 관한 법률 제2조제1호의3)</t>
         </is>
       </c>
       <c r="C40" s="6" t="n">
@@ -28871,24 +28871,24 @@
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>안전</t>
+          <t>학교폭력</t>
         </is>
       </c>
       <c r="E40" s="12" t="inlineStr">
         <is>
-          <t>https://www.kacpr.org/page/page.php?category_idx=3&amp;category1_code=1247206302&amp;category2_code=1527742406&amp;page_idx=1118</t>
+          <t>https://www.easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=1408&amp;ccfNo=1&amp;cciNo=1&amp;cnpClsNo=1</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="14" t="inlineStr">
         <is>
-          <t>법제처(찾기쉬운 생활법령정보)</t>
+          <t>행정안전부</t>
         </is>
       </c>
       <c r="B41" s="14" t="inlineStr">
         <is>
-          <t>학교폭력 &gt; 학교폭력의 이해 &gt; 학교폭력의 개념 (학교폭력예방 및 대책에 관한 법률 제2조제1호의3)</t>
+          <t>어린이 안전 배움터 - 소방·안전(화재 발생 시 요령)</t>
         </is>
       </c>
       <c r="C41" s="13" t="n">
@@ -28896,12 +28896,12 @@
       </c>
       <c r="D41" s="14" t="inlineStr">
         <is>
-          <t>학교폭력</t>
+          <t>안전</t>
         </is>
       </c>
       <c r="E41" s="15" t="inlineStr">
         <is>
-          <t>https://www.easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=1408&amp;ccfNo=1&amp;cciNo=1&amp;cnpClsNo=1</t>
+          <t>https://www.mois.go.kr/chd/sub/a06/fire/screen.do</t>
         </is>
       </c>
     </row>
@@ -28913,7 +28913,7 @@
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>어린이 안전 배움터 - 소방·안전(화재 발생 시 요령)</t>
+          <t>어린이 안전 배움터 - 소화기 사용법과 화재신고</t>
         </is>
       </c>
       <c r="C42" s="6" t="n">
@@ -28926,7 +28926,7 @@
       </c>
       <c r="E42" s="12" t="inlineStr">
         <is>
-          <t>https://www.mois.go.kr/chd/sub/a06/fire/screen.do</t>
+          <t>https://www.mois.go.kr/chd/sub/a06/fire_2/screen.do</t>
         </is>
       </c>
     </row>
@@ -28938,7 +28938,7 @@
       </c>
       <c r="B43" s="14" t="inlineStr">
         <is>
-          <t>어린이 안전 배움터 - 소화기 사용법과 화재신고</t>
+          <t>어린이 안전 배움터 - 놀이기구(놀이터 안전)</t>
         </is>
       </c>
       <c r="C43" s="13" t="n">
@@ -28951,7 +28951,7 @@
       </c>
       <c r="E43" s="15" t="inlineStr">
         <is>
-          <t>https://www.mois.go.kr/chd/sub/a06/fire_2/screen.do</t>
+          <t>https://www.mois.go.kr/chd/sub/a06/play_2/screen.do</t>
         </is>
       </c>
     </row>
@@ -28963,7 +28963,7 @@
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>어린이 안전 배움터 - 놀이기구(놀이터 안전)</t>
+          <t>국민안전24(옛 국민재난안전포털) - 태풍 국민행동요령</t>
         </is>
       </c>
       <c r="C44" s="6" t="n">
@@ -28976,7 +28976,7 @@
       </c>
       <c r="E44" s="12" t="inlineStr">
         <is>
-          <t>https://www.mois.go.kr/chd/sub/a06/play_2/screen.do</t>
+          <t>https://www.safekorea.go.kr/safekorea-kor/acts/nacts/action-guide.do?category=typhoon&amp;actsHeaderTitle=%ED%83%9C%ED%92%8D&amp;menuSn=4</t>
         </is>
       </c>
     </row>
@@ -28988,7 +28988,7 @@
       </c>
       <c r="B45" s="14" t="inlineStr">
         <is>
-          <t>국민안전24(옛 국민재난안전포털) - 태풍 국민행동요령</t>
+          <t>어린이 안전 배움터 - 여름철 안전(물놀이)</t>
         </is>
       </c>
       <c r="C45" s="13" t="n">
@@ -29001,44 +29001,44 @@
       </c>
       <c r="E45" s="15" t="inlineStr">
         <is>
-          <t>https://www.safekorea.go.kr/safekorea-kor/acts/nacts/action-guide.do?category=typhoon&amp;actsHeaderTitle=%ED%83%9C%ED%92%8D&amp;menuSn=4</t>
+          <t>https://www.mois.go.kr/chd/sub/a06/summer/screen.do</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>행정안전부</t>
+          <t>법제처(찾기쉬운 생활법령정보)</t>
         </is>
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>어린이 안전 배움터 - 여름철 안전(물놀이)</t>
+          <t>학교폭력 &gt; 학교폭력 신고 및 초기대응 &gt; 학교폭력의 신고 및 고발</t>
         </is>
       </c>
       <c r="C46" s="6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>안전</t>
+          <t>학교폭력</t>
         </is>
       </c>
       <c r="E46" s="12" t="inlineStr">
         <is>
-          <t>https://www.mois.go.kr/chd/sub/a06/summer/screen.do</t>
+          <t>https://easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=1408&amp;ccfNo=3&amp;cciNo=1&amp;cnpClsNo=1</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="14" t="inlineStr">
         <is>
-          <t>법제처(찾기쉬운 생활법령정보)</t>
+          <t>한국환경보전원 탄소중립 정책포털</t>
         </is>
       </c>
       <c r="B47" s="14" t="inlineStr">
         <is>
-          <t>학교폭력 &gt; 학교폭력 신고 및 초기대응 &gt; 학교폭력의 신고 및 고발</t>
+          <t>기후변화 - 온실가스와 온실효과</t>
         </is>
       </c>
       <c r="C47" s="13" t="n">
@@ -29046,24 +29046,24 @@
       </c>
       <c r="D47" s="14" t="inlineStr">
         <is>
-          <t>학교폭력</t>
+          <t>환경</t>
         </is>
       </c>
       <c r="E47" s="15" t="inlineStr">
         <is>
-          <t>https://easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=1408&amp;ccfNo=3&amp;cciNo=1&amp;cnpClsNo=1</t>
+          <t>https://www.gihoo.or.kr/menu.es?mid=a30101010000</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>한국환경보전원 탄소중립 정책포털</t>
+          <t>행정안전부</t>
         </is>
       </c>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>기후변화 - 온실가스와 온실효과</t>
+          <t>어린이 안전 배움터 - 도로·교통(어린이보호구역 교통안전수칙)</t>
         </is>
       </c>
       <c r="C48" s="6" t="n">
@@ -29071,12 +29071,12 @@
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>환경</t>
+          <t>안전</t>
         </is>
       </c>
       <c r="E48" s="12" t="inlineStr">
         <is>
-          <t>https://www.gihoo.or.kr/menu.es?mid=a30101010000</t>
+          <t>https://www.mois.go.kr/chd/sub/a06/road/screen.do</t>
         </is>
       </c>
     </row>
@@ -29608,12 +29608,12 @@
     <row r="70">
       <c r="A70" s="7" t="inlineStr">
         <is>
-          <t>법제처(찾기쉬운 생활법령정보)</t>
+          <t>대한민국 정책브리핑(문화체육관광부 운영)</t>
         </is>
       </c>
       <c r="B70" s="7" t="inlineStr">
         <is>
-          <t>찾기쉬운 생활법령정보 - 어린이통학버스의 안전설비</t>
+          <t>새 학기, 자녀와 함께 교통안전수칙 알아봤습니다! (횡단보도 5원칙)</t>
         </is>
       </c>
       <c r="C70" s="6" t="n">
@@ -29626,7 +29626,7 @@
       </c>
       <c r="E70" s="12" t="inlineStr">
         <is>
-          <t>https://easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=690&amp;ccfNo=1&amp;cciNo=2&amp;cnpClsNo=2</t>
+          <t>https://www.korea.kr/news/policyNewsView.do?newsId=148926855</t>
         </is>
       </c>
     </row>
@@ -29638,7 +29638,7 @@
       </c>
       <c r="B71" s="14" t="inlineStr">
         <is>
-          <t>학교폭력 &gt; 학교폭력의 해결 &gt; 가해학생에 대한 조치 (학교폭력예방 및 대책에 관한 법률 제17조)</t>
+          <t>찾기쉬운 생활법령정보 - 어린이통학버스의 안전설비</t>
         </is>
       </c>
       <c r="C71" s="13" t="n">
@@ -29646,12 +29646,12 @@
       </c>
       <c r="D71" s="14" t="inlineStr">
         <is>
-          <t>학교폭력</t>
+          <t>안전</t>
         </is>
       </c>
       <c r="E71" s="15" t="inlineStr">
         <is>
-          <t>https://easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=1408&amp;ccfNo=4&amp;cciNo=2&amp;cnpClsNo=6</t>
+          <t>https://easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=690&amp;ccfNo=1&amp;cciNo=2&amp;cnpClsNo=2</t>
         </is>
       </c>
     </row>
@@ -29663,7 +29663,7 @@
       </c>
       <c r="B72" s="7" t="inlineStr">
         <is>
-          <t>청소년의 인터넷 이용하기 &gt; 댓글을 다는 경우 &gt; 인터넷 명예훼손에 대처하는 방법 (정보통신망법 제70조제1항)</t>
+          <t>학교폭력 &gt; 학교폭력의 해결 &gt; 가해학생에 대한 조치 (학교폭력예방 및 대책에 관한 법률 제17조)</t>
         </is>
       </c>
       <c r="C72" s="6" t="n">
@@ -29676,7 +29676,7 @@
       </c>
       <c r="E72" s="12" t="inlineStr">
         <is>
-          <t>https://easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=659&amp;ccfNo=6&amp;cciNo=2&amp;cnpClsNo=1</t>
+          <t>https://easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=1408&amp;ccfNo=4&amp;cciNo=2&amp;cnpClsNo=6</t>
         </is>
       </c>
     </row>
@@ -29688,7 +29688,7 @@
       </c>
       <c r="B73" s="14" t="inlineStr">
         <is>
-          <t>학교폭력 &gt; 학교폭력 신고 및 초기대응 &gt; 학교폭력의 신고 및 고발 (학교폭력예방 및 대책에 관한 법률 제20조제5항)</t>
+          <t>청소년의 인터넷 이용하기 &gt; 댓글을 다는 경우 &gt; 인터넷 명예훼손에 대처하는 방법 (정보통신망법 제70조제1항)</t>
         </is>
       </c>
       <c r="C73" s="13" t="n">
@@ -29701,19 +29701,19 @@
       </c>
       <c r="E73" s="15" t="inlineStr">
         <is>
-          <t>https://easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=1408&amp;ccfNo=3&amp;cciNo=1&amp;cnpClsNo=1</t>
+          <t>https://easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=659&amp;ccfNo=6&amp;cciNo=2&amp;cnpClsNo=1</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="inlineStr">
         <is>
-          <t>행정안전부</t>
+          <t>법제처(찾기쉬운 생활법령정보)</t>
         </is>
       </c>
       <c r="B74" s="7" t="inlineStr">
         <is>
-          <t>어린이 안전 배움터 - 구조·구급(119 구급신고요령)</t>
+          <t>학교폭력 &gt; 학교폭력 신고 및 초기대응 &gt; 학교폭력의 신고 및 고발 (학교폭력예방 및 대책에 관한 법률 제20조제5항)</t>
         </is>
       </c>
       <c r="C74" s="6" t="n">
@@ -29721,49 +29721,49 @@
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>안전</t>
+          <t>학교폭력</t>
         </is>
       </c>
       <c r="E74" s="12" t="inlineStr">
         <is>
-          <t>https://www.mois.go.kr/chd/sub/a06/rescue/screen.do</t>
+          <t>https://easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=1408&amp;ccfNo=3&amp;cciNo=1&amp;cnpClsNo=1</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="14" t="inlineStr">
         <is>
-          <t>기상청</t>
+          <t>행정안전부</t>
         </is>
       </c>
       <c r="B75" s="14" t="inlineStr">
         <is>
-          <t>보도자료 - 2025년, 다양한 이상기후로 확인된 '기후위기의 시대'</t>
+          <t>어린이 안전 배움터 - 구조·구급(119 구급신고요령)</t>
         </is>
       </c>
       <c r="C75" s="13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D75" s="14" t="inlineStr">
         <is>
-          <t>환경</t>
+          <t>안전</t>
         </is>
       </c>
       <c r="E75" s="15" t="inlineStr">
         <is>
-          <t>https://www.kma.go.kr/kma/news/press.jsp?bid=press&amp;mode=view&amp;num=1194622</t>
+          <t>https://www.mois.go.kr/chd/sub/a06/rescue/screen.do</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="7" t="inlineStr">
         <is>
-          <t>법제처(찾기쉬운 생활법령정보)</t>
+          <t>기상청</t>
         </is>
       </c>
       <c r="B76" s="7" t="inlineStr">
         <is>
-          <t>찾기쉬운 생활법령정보 - 어린이 보행사고 예방을 위한 안전수칙(도로교통법 제10조제2항)</t>
+          <t>보도자료 - 2025년, 다양한 이상기후로 확인된 '기후위기의 시대'</t>
         </is>
       </c>
       <c r="C76" s="6" t="n">
@@ -29771,12 +29771,12 @@
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>안전</t>
+          <t>환경</t>
         </is>
       </c>
       <c r="E76" s="12" t="inlineStr">
         <is>
-          <t>https://www.easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=690&amp;ccfNo=1&amp;cciNo=1&amp;cnpClsNo=1</t>
+          <t>https://www.kma.go.kr/kma/news/press.jsp?bid=press&amp;mode=view&amp;num=1194622</t>
         </is>
       </c>
     </row>
@@ -29788,7 +29788,7 @@
       </c>
       <c r="B77" s="14" t="inlineStr">
         <is>
-          <t>찾기쉬운 생활법령정보 - 어린이 자전거 안전(도로교통법 제11조제3항)</t>
+          <t>찾기쉬운 생활법령정보 - 어린이 보행사고 예방을 위한 안전수칙(도로교통법 제10조제2항)</t>
         </is>
       </c>
       <c r="C77" s="13" t="n">
@@ -29801,7 +29801,7 @@
       </c>
       <c r="E77" s="15" t="inlineStr">
         <is>
-          <t>https://www.easylaw.go.kr/CSP/CnpClsMainBtr.laf?popMenu=ov&amp;csmSeq=690&amp;ccfNo=1&amp;cciNo=3&amp;cnpClsNo=1</t>
+          <t>https://www.easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=690&amp;ccfNo=1&amp;cciNo=1&amp;cnpClsNo=1</t>
         </is>
       </c>
     </row>
@@ -29813,7 +29813,7 @@
       </c>
       <c r="B78" s="7" t="inlineStr">
         <is>
-          <t>찾기쉬운 생활법령정보 - 어린이 자전거 안전(도로교통법 제13조의2제6항)</t>
+          <t>찾기쉬운 생활법령정보 - 어린이 자전거 안전(도로교통법 제11조제3항)</t>
         </is>
       </c>
       <c r="C78" s="6" t="n">
@@ -29838,7 +29838,7 @@
       </c>
       <c r="B79" s="14" t="inlineStr">
         <is>
-          <t>찾기쉬운 생활법령정보 - 어린이 생활안전(어린이 보호구역)</t>
+          <t>찾기쉬운 생활법령정보 - 어린이 자전거 안전(도로교통법 제13조의2제6항)</t>
         </is>
       </c>
       <c r="C79" s="13" t="n">
@@ -29851,7 +29851,7 @@
       </c>
       <c r="E79" s="15" t="inlineStr">
         <is>
-          <t>https://www.easylaw.go.kr/CSP/CnpClsMainBtr.laf?popMenu=ov&amp;csmSeq=690&amp;ccfNo=1&amp;cciNo=1&amp;cnpClsNo=3</t>
+          <t>https://www.easylaw.go.kr/CSP/CnpClsMainBtr.laf?popMenu=ov&amp;csmSeq=690&amp;ccfNo=1&amp;cciNo=3&amp;cnpClsNo=1</t>
         </is>
       </c>
     </row>
@@ -29863,7 +29863,7 @@
       </c>
       <c r="B80" s="7" t="inlineStr">
         <is>
-          <t>찾기쉬운 생활법령정보 - 가정의 차량 탑승 시 안전수칙(도로교통법 제50조제1항)</t>
+          <t>찾기쉬운 생활법령정보 - 어린이 생활안전(어린이 보호구역)</t>
         </is>
       </c>
       <c r="C80" s="6" t="n">
@@ -29876,7 +29876,7 @@
       </c>
       <c r="E80" s="12" t="inlineStr">
         <is>
-          <t>https://easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=690&amp;ccfNo=1&amp;cciNo=2&amp;cnpClsNo=1</t>
+          <t>https://www.easylaw.go.kr/CSP/CnpClsMainBtr.laf?popMenu=ov&amp;csmSeq=690&amp;ccfNo=1&amp;cciNo=1&amp;cnpClsNo=3</t>
         </is>
       </c>
     </row>
@@ -29888,7 +29888,7 @@
       </c>
       <c r="B81" s="14" t="inlineStr">
         <is>
-          <t>찾기쉬운 생활법령정보 - 가정의 차량 탑승 시 안전수칙(도로교통법 제49조제1항제7호)</t>
+          <t>찾기쉬운 생활법령정보 - 가정의 차량 탑승 시 안전수칙(도로교통법 제50조제1항)</t>
         </is>
       </c>
       <c r="C81" s="13" t="n">
@@ -29913,7 +29913,7 @@
       </c>
       <c r="B82" s="7" t="inlineStr">
         <is>
-          <t>찾기쉬운 생활법령정보 - 화재예방을 위한 안전수칙(화상 응급처치)</t>
+          <t>찾기쉬운 생활법령정보 - 가정의 차량 탑승 시 안전수칙(도로교통법 제49조제1항제7호)</t>
         </is>
       </c>
       <c r="C82" s="6" t="n">
@@ -29926,7 +29926,7 @@
       </c>
       <c r="E82" s="12" t="inlineStr">
         <is>
-          <t>https://easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=690&amp;ccfNo=5&amp;cciNo=1&amp;cnpClsNo=1</t>
+          <t>https://easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=690&amp;ccfNo=1&amp;cciNo=2&amp;cnpClsNo=1</t>
         </is>
       </c>
     </row>
@@ -29938,7 +29938,7 @@
       </c>
       <c r="B83" s="14" t="inlineStr">
         <is>
-          <t>학교폭력 &gt; 사전예방 &gt; 학교폭력 예방교육 실시 (학교폭력예방 및 대책에 관한 법률 제15조)</t>
+          <t>찾기쉬운 생활법령정보 - 화재예방을 위한 안전수칙(화상 응급처치)</t>
         </is>
       </c>
       <c r="C83" s="13" t="n">
@@ -29946,12 +29946,12 @@
       </c>
       <c r="D83" s="14" t="inlineStr">
         <is>
-          <t>학교폭력</t>
+          <t>안전</t>
         </is>
       </c>
       <c r="E83" s="15" t="inlineStr">
         <is>
-          <t>https://www.easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=1408&amp;ccfNo=2&amp;cciNo=2&amp;cnpClsNo=1</t>
+          <t>https://easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=690&amp;ccfNo=5&amp;cciNo=1&amp;cnpClsNo=1</t>
         </is>
       </c>
     </row>
@@ -29963,7 +29963,7 @@
       </c>
       <c r="B84" s="7" t="inlineStr">
         <is>
-          <t>학교폭력 &gt; 학교폭력 신고 및 초기대응 &gt; 학교폭력의 신고 및 고발 (학교폭력예방 및 대책에 관한 법률 제20조)</t>
+          <t>학교폭력 &gt; 사전예방 &gt; 학교폭력 예방교육 실시 (학교폭력예방 및 대책에 관한 법률 제15조)</t>
         </is>
       </c>
       <c r="C84" s="6" t="n">
@@ -29976,7 +29976,7 @@
       </c>
       <c r="E84" s="12" t="inlineStr">
         <is>
-          <t>https://easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=1408&amp;ccfNo=3&amp;cciNo=1&amp;cnpClsNo=1</t>
+          <t>https://www.easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=1408&amp;ccfNo=2&amp;cciNo=2&amp;cnpClsNo=1</t>
         </is>
       </c>
     </row>
@@ -29988,7 +29988,7 @@
       </c>
       <c r="B85" s="14" t="inlineStr">
         <is>
-          <t>학교폭력 &gt; 학교폭력의 해결 &gt; 가해학생에 대한 조치 (학교폭력예방 및 대책에 관한 법률 제17조제1항제2호)</t>
+          <t>학교폭력 &gt; 학교폭력 신고 및 초기대응 &gt; 학교폭력의 신고 및 고발 (학교폭력예방 및 대책에 관한 법률 제20조)</t>
         </is>
       </c>
       <c r="C85" s="13" t="n">
@@ -30001,7 +30001,7 @@
       </c>
       <c r="E85" s="15" t="inlineStr">
         <is>
-          <t>https://easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=1408&amp;ccfNo=4&amp;cciNo=2&amp;cnpClsNo=6</t>
+          <t>https://easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=1408&amp;ccfNo=3&amp;cciNo=1&amp;cnpClsNo=1</t>
         </is>
       </c>
     </row>
@@ -30013,7 +30013,7 @@
       </c>
       <c r="B86" s="7" t="inlineStr">
         <is>
-          <t>학교폭력 &gt; 학교폭력 신고 및 초기대응 &gt; 학교폭력의 신고 및 고발 (학교폭력예방 및 대책에 관한 법률 제20조제4항)</t>
+          <t>학교폭력 &gt; 학교폭력의 해결 &gt; 가해학생에 대한 조치 (학교폭력예방 및 대책에 관한 법률 제17조제1항제2호)</t>
         </is>
       </c>
       <c r="C86" s="6" t="n">
@@ -30026,7 +30026,7 @@
       </c>
       <c r="E86" s="12" t="inlineStr">
         <is>
-          <t>https://easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=1408&amp;ccfNo=3&amp;cciNo=1&amp;cnpClsNo=1</t>
+          <t>https://easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=1408&amp;ccfNo=4&amp;cciNo=2&amp;cnpClsNo=6</t>
         </is>
       </c>
     </row>
@@ -30038,7 +30038,7 @@
       </c>
       <c r="B87" s="14" t="inlineStr">
         <is>
-          <t>학교폭력 &gt; 학교폭력 신고 및 초기대응 &gt; 학교폭력의 신고 및 고발 (학교폭력예방 및 대책에 관한 법률 제21조)</t>
+          <t>학교폭력 &gt; 학교폭력 신고 및 초기대응 &gt; 학교폭력의 신고 및 고발 (학교폭력예방 및 대책에 관한 법률 제20조제4항)</t>
         </is>
       </c>
       <c r="C87" s="13" t="n">
@@ -30051,7 +30051,7 @@
       </c>
       <c r="E87" s="15" t="inlineStr">
         <is>
-          <t>https://www.easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=1408&amp;ccfNo=3&amp;cciNo=1&amp;cnpClsNo=1&amp;menuType=onhunqna</t>
+          <t>https://easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=1408&amp;ccfNo=3&amp;cciNo=1&amp;cnpClsNo=1</t>
         </is>
       </c>
     </row>
@@ -30063,7 +30063,7 @@
       </c>
       <c r="B88" s="7" t="inlineStr">
         <is>
-          <t>학교폭력 &gt; 학교폭력의 해결 &gt; 가해학생에 대한 조치 (학교폭력예방 및 대책에 관한 법률 제17조제1항제1호)</t>
+          <t>학교폭력 &gt; 학교폭력 신고 및 초기대응 &gt; 학교폭력의 신고 및 고발 (학교폭력예방 및 대책에 관한 법률 제21조)</t>
         </is>
       </c>
       <c r="C88" s="6" t="n">
@@ -30076,19 +30076,19 @@
       </c>
       <c r="E88" s="12" t="inlineStr">
         <is>
-          <t>https://easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=1408&amp;ccfNo=4&amp;cciNo=2&amp;cnpClsNo=6</t>
+          <t>https://www.easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=1408&amp;ccfNo=3&amp;cciNo=1&amp;cnpClsNo=1&amp;menuType=onhunqna</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="14" t="inlineStr">
         <is>
-          <t>푸른나무재단</t>
+          <t>법제처(찾기쉬운 생활법령정보)</t>
         </is>
       </c>
       <c r="B89" s="14" t="inlineStr">
         <is>
-          <t>푸른나무재단 청소년 전문 상담·지원 안내</t>
+          <t>학교폭력 &gt; 학교폭력의 해결 &gt; 가해학생에 대한 조치 (학교폭력예방 및 대책에 관한 법률 제17조제1항제1호)</t>
         </is>
       </c>
       <c r="C89" s="13" t="n">
@@ -30101,19 +30101,19 @@
       </c>
       <c r="E89" s="15" t="inlineStr">
         <is>
-          <t>https://btf.or.kr/business/bus01.asp?scrID=0000000108&amp;pageNum=3&amp;subNum=1&amp;ssubNum=1</t>
+          <t>https://easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=1408&amp;ccfNo=4&amp;cciNo=2&amp;cnpClsNo=6</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="7" t="inlineStr">
         <is>
-          <t>한국환경보전원 탄소중립 정책포털</t>
+          <t>푸른나무재단</t>
         </is>
       </c>
       <c r="B90" s="7" t="inlineStr">
         <is>
-          <t>우리나라 기후변화</t>
+          <t>푸른나무재단 청소년 전문 상담·지원 안내</t>
         </is>
       </c>
       <c r="C90" s="6" t="n">
@@ -30121,24 +30121,24 @@
       </c>
       <c r="D90" s="7" t="inlineStr">
         <is>
-          <t>환경</t>
+          <t>학교폭력</t>
         </is>
       </c>
       <c r="E90" s="12" t="inlineStr">
         <is>
-          <t>https://www.gihoo.or.kr/menu.es?mid=a30101030000</t>
+          <t>https://btf.or.kr/business/bus01.asp?scrID=0000000108&amp;pageNum=3&amp;subNum=1&amp;ssubNum=1</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="14" t="inlineStr">
         <is>
-          <t>행정안전부</t>
+          <t>한국환경보전원 탄소중립 정책포털</t>
         </is>
       </c>
       <c r="B91" s="14" t="inlineStr">
         <is>
-          <t>어린이 안전 배움터 - 구조·구급(심폐소생술)</t>
+          <t>우리나라 기후변화</t>
         </is>
       </c>
       <c r="C91" s="13" t="n">
@@ -30146,49 +30146,49 @@
       </c>
       <c r="D91" s="14" t="inlineStr">
         <is>
-          <t>안전</t>
+          <t>환경</t>
         </is>
       </c>
       <c r="E91" s="15" t="inlineStr">
         <is>
-          <t>https://www.mois.go.kr/chd/sub/a06/rescue_3/screen.do</t>
+          <t>https://www.gihoo.or.kr/menu.es?mid=a30101030000</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="7" t="inlineStr">
         <is>
-          <t>교육부</t>
+          <t>행정안전부</t>
         </is>
       </c>
       <c r="B92" s="7" t="inlineStr">
         <is>
-          <t>초1·2 학폭 심의 전 '관계회복 프로그램' 우선 실시 (정책브리핑, 2025.4.30.)</t>
+          <t>어린이 안전 배움터 - 구조·구급(심폐소생술)</t>
         </is>
       </c>
       <c r="C92" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D92" s="7" t="inlineStr">
         <is>
-          <t>학교폭력</t>
+          <t>안전</t>
         </is>
       </c>
       <c r="E92" s="12" t="inlineStr">
         <is>
-          <t>https://www.korea.kr/news/policyNewsView.do?newsId=148942634</t>
+          <t>https://www.mois.go.kr/chd/sub/a06/rescue_3/screen.do</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="14" t="inlineStr">
         <is>
-          <t>법제처(찾기쉬운 생활법령정보)</t>
+          <t>교육부</t>
         </is>
       </c>
       <c r="B93" s="14" t="inlineStr">
         <is>
-          <t>찾기쉬운 생활법령정보 - 어린이 자전거 안전(도로교통법 제13조의2제2항)</t>
+          <t>초1·2 학폭 심의 전 '관계회복 프로그램' 우선 실시 (정책브리핑, 2025.4.30.)</t>
         </is>
       </c>
       <c r="C93" s="13" t="n">
@@ -30196,24 +30196,24 @@
       </c>
       <c r="D93" s="14" t="inlineStr">
         <is>
-          <t>안전</t>
+          <t>학교폭력</t>
         </is>
       </c>
       <c r="E93" s="15" t="inlineStr">
         <is>
-          <t>https://www.easylaw.go.kr/CSP/CnpClsMainBtr.laf?popMenu=ov&amp;csmSeq=690&amp;ccfNo=1&amp;cciNo=3&amp;cnpClsNo=1</t>
+          <t>https://www.korea.kr/news/policyNewsView.do?newsId=148942634</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="7" t="inlineStr">
         <is>
-          <t>법제처(찾기쉬운 생활법령정보)</t>
+          <t>대한민국 정책브리핑(문화체육관광부 운영)</t>
         </is>
       </c>
       <c r="B94" s="7" t="inlineStr">
         <is>
-          <t>학교폭력 &gt; 학교폭력의 이해 &gt; 학교폭력의 개념 (학교폭력예방 및 대책에 관한 법률 제2조)</t>
+          <t>어린이 교통안전 수칙을 지켜라</t>
         </is>
       </c>
       <c r="C94" s="6" t="n">
@@ -30221,10 +30221,60 @@
       </c>
       <c r="D94" s="7" t="inlineStr">
         <is>
+          <t>안전</t>
+        </is>
+      </c>
+      <c r="E94" s="12" t="inlineStr">
+        <is>
+          <t>https://www.korea.kr/news/policyNewsView.do?newsId=148954485</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="14" t="inlineStr">
+        <is>
+          <t>법제처(찾기쉬운 생활법령정보)</t>
+        </is>
+      </c>
+      <c r="B95" s="14" t="inlineStr">
+        <is>
+          <t>찾기쉬운 생활법령정보 - 어린이 자전거 안전(도로교통법 제13조의2제2항)</t>
+        </is>
+      </c>
+      <c r="C95" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D95" s="14" t="inlineStr">
+        <is>
+          <t>안전</t>
+        </is>
+      </c>
+      <c r="E95" s="15" t="inlineStr">
+        <is>
+          <t>https://www.easylaw.go.kr/CSP/CnpClsMainBtr.laf?popMenu=ov&amp;csmSeq=690&amp;ccfNo=1&amp;cciNo=3&amp;cnpClsNo=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="7" t="inlineStr">
+        <is>
+          <t>법제처(찾기쉬운 생활법령정보)</t>
+        </is>
+      </c>
+      <c r="B96" s="7" t="inlineStr">
+        <is>
+          <t>학교폭력 &gt; 학교폭력의 이해 &gt; 학교폭력의 개념 (학교폭력예방 및 대책에 관한 법률 제2조)</t>
+        </is>
+      </c>
+      <c r="C96" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D96" s="7" t="inlineStr">
+        <is>
           <t>학교폭력</t>
         </is>
       </c>
-      <c r="E94" s="12" t="inlineStr">
+      <c r="E96" s="12" t="inlineStr">
         <is>
           <t>https://www.easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=1408&amp;ccfNo=1&amp;cciNo=1&amp;cnpClsNo=1</t>
         </is>
@@ -30301,6 +30351,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E92" r:id="rId67"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E93" r:id="rId68"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E94" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E95" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E96" r:id="rId71"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/quiz/수업도우미_퀴즈_문항과출처.xlsx
+++ b/quiz/수업도우미_퀴즈_문항과출처.xlsx
@@ -11095,7 +11095,7 @@
       </c>
       <c r="B103" s="7" t="inlineStr">
         <is>
-          <t>소화기는 창고 안쪽 깊숙한 곳에 넣어 두는 것이 좋아요.</t>
+          <t>화상을 입은 곳에는 열이 식기 전에 연고를 발라 주면 좋아요.</t>
         </is>
       </c>
       <c r="C103" s="6" t="inlineStr">
@@ -11105,7 +11105,7 @@
       </c>
       <c r="D103" s="7" t="inlineStr">
         <is>
-          <t>아니요! 눈에 잘 띄고 바로 꺼낼 수 있는 곳에 두어야 해요.</t>
+          <t>틀려요! 열이 식기 전에는 연고를 바르지 않아요.</t>
         </is>
       </c>
       <c r="E103" s="7" t="inlineStr">
@@ -11120,7 +11120,7 @@
       </c>
       <c r="G103" s="7" t="inlineStr">
         <is>
-          <t>찾기쉬운 생활법령정보 - 화재예방을 위한 안전수칙</t>
+          <t>찾기쉬운 생활법령정보 - 화재예방을 위한 안전수칙(화상 응급처치)</t>
         </is>
       </c>
       <c r="H103" s="12" t="inlineStr">
@@ -11215,17 +11215,17 @@
       </c>
       <c r="B106" s="14" t="inlineStr">
         <is>
-          <t>비상구 앞에 물건을 쌓아 두어도 대피에는 지장이 없어요.</t>
+          <t>데인 곳을 찬물에 10분 넘게 계속 대고 있으면 체온이 떨어질 수 있어요.</t>
         </is>
       </c>
       <c r="C106" s="13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="D106" s="14" t="inlineStr">
         <is>
-          <t>아니요! 비상구가 막히면 급할 때 빠져나갈 수 없어요.</t>
+          <t>맞아요! 너무 오래 대고 있으면 몸이 차가워질 수 있어요.</t>
         </is>
       </c>
       <c r="E106" s="14" t="inlineStr">
@@ -11240,7 +11240,7 @@
       </c>
       <c r="G106" s="14" t="inlineStr">
         <is>
-          <t>찾기쉬운 생활법령정보 - 화재예방을 위한 안전수칙</t>
+          <t>찾기쉬운 생활법령정보 - 화재예방을 위한 안전수칙(화상 응급처치)</t>
         </is>
       </c>
       <c r="H106" s="15" t="inlineStr">
@@ -11305,7 +11305,7 @@
       </c>
       <c r="D108" s="14" t="inlineStr">
         <is>
-          <t>틀려요! 전선이 상해 불이 날 수 있으니 플러그 몸통을 잡아요.</t>
+          <t>틀려요! 전기코드는 반드시 플러그를 잡고 뽑아야 해요.</t>
         </is>
       </c>
       <c r="E108" s="14" t="inlineStr">
@@ -11315,17 +11315,17 @@
       </c>
       <c r="F108" s="14" t="inlineStr">
         <is>
-          <t>법제처(찾기쉬운 생활법령정보)</t>
+          <t>행정안전부</t>
         </is>
       </c>
       <c r="G108" s="14" t="inlineStr">
         <is>
-          <t>찾기쉬운 생활법령정보 - 화재예방을 위한 안전수칙</t>
+          <t>국민안전24 - 전기·가스 사고 국민행동요령</t>
         </is>
       </c>
       <c r="H108" s="15" t="inlineStr">
         <is>
-          <t>https://easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=690&amp;ccfNo=5&amp;cciNo=1&amp;cnpClsNo=1</t>
+          <t>https://www.safekorea.go.kr/safekorea-kor/acts/nacts/action-guide.do?category=electircGasAccident&amp;actsHeaderTitle=%EC%A0%84%EA%B8%B0%C2%B7%EA%B0%80%EC%8A%A4+%EC%82%AC%EA%B3%A0&amp;menuSn=4</t>
         </is>
       </c>
     </row>
@@ -11335,7 +11335,7 @@
       </c>
       <c r="B109" s="7" t="inlineStr">
         <is>
-          <t>전기장판은 접거나 무거운 것을 올려 두면 안 돼요.</t>
+          <t>소방차가 다니는 길을 막거나 불 끄는 일을 방해하는 물건을 두면 안 돼요.</t>
         </is>
       </c>
       <c r="C109" s="6" t="inlineStr">
@@ -11345,7 +11345,7 @@
       </c>
       <c r="D109" s="7" t="inlineStr">
         <is>
-          <t>맞아요! 안쪽 열선이 끊어져 불이 날 수 있어요.</t>
+          <t>맞아요! 소방 활동을 방해하는 물건은 치워 두어야 해요.</t>
         </is>
       </c>
       <c r="E109" s="7" t="inlineStr">
@@ -11360,7 +11360,7 @@
       </c>
       <c r="G109" s="7" t="inlineStr">
         <is>
-          <t>찾기쉬운 생활법령정보 - 화재예방을 위한 안전수칙</t>
+          <t>찾기쉬운 생활법령정보 - 화재예방을 위한 안전수칙(화상 응급처치)</t>
         </is>
       </c>
       <c r="H109" s="12" t="inlineStr">
@@ -11385,7 +11385,7 @@
       </c>
       <c r="D110" s="14" t="inlineStr">
         <is>
-          <t>아니요! 작은 불꽃에도 폭발할 수 있으니 밸브를 잠그고 창문을 열어요.</t>
+          <t>아니요! 가스가 샐 때는 전기기구를 절대 조작하면 안 돼요.</t>
         </is>
       </c>
       <c r="E110" s="14" t="inlineStr">
@@ -11395,17 +11395,17 @@
       </c>
       <c r="F110" s="14" t="inlineStr">
         <is>
-          <t>법제처(찾기쉬운 생활법령정보)</t>
+          <t>행정안전부</t>
         </is>
       </c>
       <c r="G110" s="14" t="inlineStr">
         <is>
-          <t>찾기쉬운 생활법령정보 - 화재예방을 위한 안전수칙</t>
+          <t>국민안전24 - 전기·가스 사고 국민행동요령</t>
         </is>
       </c>
       <c r="H110" s="15" t="inlineStr">
         <is>
-          <t>https://easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=690&amp;ccfNo=5&amp;cciNo=1&amp;cnpClsNo=1</t>
+          <t>https://www.safekorea.go.kr/safekorea-kor/acts/nacts/action-guide.do?category=electircGasAccident&amp;actsHeaderTitle=%EC%A0%84%EA%B8%B0%C2%B7%EA%B0%80%EC%8A%A4+%EC%82%AC%EA%B3%A0&amp;menuSn=4</t>
         </is>
       </c>
     </row>
@@ -11735,17 +11735,17 @@
       </c>
       <c r="B119" s="7" t="inlineStr">
         <is>
-          <t>데인 곳에는 된장이나 소주 같은 것을 발라 주면 빨리 나아요.</t>
+          <t>가슴압박 깊이는 어린이에게는 4~5센티미터예요.</t>
         </is>
       </c>
       <c r="C119" s="6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="D119" s="7" t="inlineStr">
         <is>
-          <t>틀려요! 상처가 덧날 수 있으니 흐르는 찬물로 식혀야 해요.</t>
+          <t>맞아요! 어른은 약 5cm, 소아는 4~5cm 깊이로 눌러요.</t>
         </is>
       </c>
       <c r="E119" s="7" t="inlineStr">
@@ -11755,17 +11755,17 @@
       </c>
       <c r="F119" s="7" t="inlineStr">
         <is>
-          <t>질병관리청</t>
+          <t>대한심폐소생협회</t>
         </is>
       </c>
       <c r="G119" s="7" t="inlineStr">
         <is>
-          <t>국가건강정보포털 - 화상</t>
+          <t>심폐소생술 시행방법</t>
         </is>
       </c>
       <c r="H119" s="12" t="inlineStr">
         <is>
-          <t>https://health.kdca.go.kr/healthinfo/biz/health/gnrlzHealthInfo/gnrlzHealthInfo/gnrlzHealthInfoView.do?cntnts_sn=6584</t>
+          <t>https://www.kacpr.org/page/page.php?category_idx=3&amp;category1_code=1247206302&amp;category2_code=1527742406&amp;page_idx=1118</t>
         </is>
       </c>
     </row>
@@ -11775,7 +11775,7 @@
       </c>
       <c r="B120" s="14" t="inlineStr">
         <is>
-          <t>데인 곳에 얼음을 직접 대고 오래 두면 더 좋아요.</t>
+          <t>데인 곳은 찬물에 1~2분만 담갔다 빼면 충분해요.</t>
         </is>
       </c>
       <c r="C120" s="13" t="inlineStr">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="D120" s="14" t="inlineStr">
         <is>
-          <t>아니요! 얼음을 직접 대면 조직이 상할 수 있어요.</t>
+          <t>틀려요! 흐르는 찬물로 20분 이상 식혀야 해요.</t>
         </is>
       </c>
       <c r="E120" s="14" t="inlineStr">
@@ -28184,7 +28184,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E96"/>
+  <dimension ref="A1:E97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -28239,7 +28239,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C6" s="16">
         <f>B6/$B$22</f>
@@ -28267,7 +28267,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C8" s="16">
         <f>B8/$B$22</f>
@@ -28389,7 +28389,7 @@
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
         <is>
-          <t>질병관리청</t>
+          <t>대한심폐소생협회</t>
         </is>
       </c>
       <c r="B17" s="13" t="n">
@@ -28403,7 +28403,7 @@
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>대한심폐소생협회</t>
+          <t>질병관리청</t>
         </is>
       </c>
       <c r="B18" s="6" t="n">
@@ -28474,7 +28474,7 @@
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t>문서별 (71종)</t>
+          <t>문서별 (72종)</t>
         </is>
       </c>
     </row>
@@ -28733,12 +28733,12 @@
     <row r="35">
       <c r="A35" s="14" t="inlineStr">
         <is>
-          <t>법제처(찾기쉬운 생활법령정보)</t>
+          <t>식품의약품안전처</t>
         </is>
       </c>
       <c r="B35" s="14" t="inlineStr">
         <is>
-          <t>찾기쉬운 생활법령정보 - 화재예방을 위한 안전수칙</t>
+          <t>서울지방식품의약품안전청 - 식중독 예방 6대 요령</t>
         </is>
       </c>
       <c r="C35" s="13" t="n">
@@ -28751,44 +28751,44 @@
       </c>
       <c r="E35" s="15" t="inlineStr">
         <is>
-          <t>https://easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=690&amp;ccfNo=5&amp;cciNo=1&amp;cnpClsNo=1</t>
+          <t>https://www.mfds.go.kr/brd/m_827/view.do?seq=3609</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>식품의약품안전처</t>
+          <t>대한민국 정책브리핑(문화체육관광부 운영)</t>
         </is>
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>서울지방식품의약품안전청 - 식중독 예방 6대 요령</t>
+          <t>올바른 분리배출의 기준, 네 가지</t>
         </is>
       </c>
       <c r="C36" s="6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>안전</t>
+          <t>환경</t>
         </is>
       </c>
       <c r="E36" s="12" t="inlineStr">
         <is>
-          <t>https://www.mfds.go.kr/brd/m_827/view.do?seq=3609</t>
+          <t>https://www.korea.kr/news/policyNewsView.do?newsId=148942053</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="14" t="inlineStr">
         <is>
-          <t>대한민국 정책브리핑(문화체육관광부 운영)</t>
+          <t>대한심폐소생협회</t>
         </is>
       </c>
       <c r="B37" s="14" t="inlineStr">
         <is>
-          <t>올바른 분리배출의 기준, 네 가지</t>
+          <t>심폐소생술 시행방법</t>
         </is>
       </c>
       <c r="C37" s="13" t="n">
@@ -28796,12 +28796,12 @@
       </c>
       <c r="D37" s="14" t="inlineStr">
         <is>
-          <t>환경</t>
+          <t>안전</t>
         </is>
       </c>
       <c r="E37" s="15" t="inlineStr">
         <is>
-          <t>https://www.korea.kr/news/policyNewsView.do?newsId=148942053</t>
+          <t>https://www.kacpr.org/page/page.php?category_idx=3&amp;category1_code=1247206302&amp;category2_code=1527742406&amp;page_idx=1118</t>
         </is>
       </c>
     </row>
@@ -28833,12 +28833,12 @@
     <row r="39">
       <c r="A39" s="14" t="inlineStr">
         <is>
-          <t>대한심폐소생협회</t>
+          <t>법제처(찾기쉬운 생활법령정보)</t>
         </is>
       </c>
       <c r="B39" s="14" t="inlineStr">
         <is>
-          <t>심폐소생술 시행방법</t>
+          <t>학교폭력 &gt; 학교폭력의 이해 &gt; 학교폭력의 개념 (학교폭력예방 및 대책에 관한 법률 제2조제1호의3)</t>
         </is>
       </c>
       <c r="C39" s="13" t="n">
@@ -28846,24 +28846,24 @@
       </c>
       <c r="D39" s="14" t="inlineStr">
         <is>
-          <t>안전</t>
+          <t>학교폭력</t>
         </is>
       </c>
       <c r="E39" s="15" t="inlineStr">
         <is>
-          <t>https://www.kacpr.org/page/page.php?category_idx=3&amp;category1_code=1247206302&amp;category2_code=1527742406&amp;page_idx=1118</t>
+          <t>https://www.easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=1408&amp;ccfNo=1&amp;cciNo=1&amp;cnpClsNo=1</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>법제처(찾기쉬운 생활법령정보)</t>
+          <t>행정안전부</t>
         </is>
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>학교폭력 &gt; 학교폭력의 이해 &gt; 학교폭력의 개념 (학교폭력예방 및 대책에 관한 법률 제2조제1호의3)</t>
+          <t>어린이 안전 배움터 - 소방·안전(화재 발생 시 요령)</t>
         </is>
       </c>
       <c r="C40" s="6" t="n">
@@ -28871,12 +28871,12 @@
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>학교폭력</t>
+          <t>안전</t>
         </is>
       </c>
       <c r="E40" s="12" t="inlineStr">
         <is>
-          <t>https://www.easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=1408&amp;ccfNo=1&amp;cciNo=1&amp;cnpClsNo=1</t>
+          <t>https://www.mois.go.kr/chd/sub/a06/fire/screen.do</t>
         </is>
       </c>
     </row>
@@ -28888,7 +28888,7 @@
       </c>
       <c r="B41" s="14" t="inlineStr">
         <is>
-          <t>어린이 안전 배움터 - 소방·안전(화재 발생 시 요령)</t>
+          <t>어린이 안전 배움터 - 소화기 사용법과 화재신고</t>
         </is>
       </c>
       <c r="C41" s="13" t="n">
@@ -28901,7 +28901,7 @@
       </c>
       <c r="E41" s="15" t="inlineStr">
         <is>
-          <t>https://www.mois.go.kr/chd/sub/a06/fire/screen.do</t>
+          <t>https://www.mois.go.kr/chd/sub/a06/fire_2/screen.do</t>
         </is>
       </c>
     </row>
@@ -28913,7 +28913,7 @@
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>어린이 안전 배움터 - 소화기 사용법과 화재신고</t>
+          <t>어린이 안전 배움터 - 놀이기구(놀이터 안전)</t>
         </is>
       </c>
       <c r="C42" s="6" t="n">
@@ -28926,7 +28926,7 @@
       </c>
       <c r="E42" s="12" t="inlineStr">
         <is>
-          <t>https://www.mois.go.kr/chd/sub/a06/fire_2/screen.do</t>
+          <t>https://www.mois.go.kr/chd/sub/a06/play_2/screen.do</t>
         </is>
       </c>
     </row>
@@ -28938,7 +28938,7 @@
       </c>
       <c r="B43" s="14" t="inlineStr">
         <is>
-          <t>어린이 안전 배움터 - 놀이기구(놀이터 안전)</t>
+          <t>국민안전24(옛 국민재난안전포털) - 태풍 국민행동요령</t>
         </is>
       </c>
       <c r="C43" s="13" t="n">
@@ -28951,7 +28951,7 @@
       </c>
       <c r="E43" s="15" t="inlineStr">
         <is>
-          <t>https://www.mois.go.kr/chd/sub/a06/play_2/screen.do</t>
+          <t>https://www.safekorea.go.kr/safekorea-kor/acts/nacts/action-guide.do?category=typhoon&amp;actsHeaderTitle=%ED%83%9C%ED%92%8D&amp;menuSn=4</t>
         </is>
       </c>
     </row>
@@ -28963,7 +28963,7 @@
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>국민안전24(옛 국민재난안전포털) - 태풍 국민행동요령</t>
+          <t>어린이 안전 배움터 - 여름철 안전(물놀이)</t>
         </is>
       </c>
       <c r="C44" s="6" t="n">
@@ -28976,44 +28976,44 @@
       </c>
       <c r="E44" s="12" t="inlineStr">
         <is>
-          <t>https://www.safekorea.go.kr/safekorea-kor/acts/nacts/action-guide.do?category=typhoon&amp;actsHeaderTitle=%ED%83%9C%ED%92%8D&amp;menuSn=4</t>
+          <t>https://www.mois.go.kr/chd/sub/a06/summer/screen.do</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="14" t="inlineStr">
         <is>
-          <t>행정안전부</t>
+          <t>법제처(찾기쉬운 생활법령정보)</t>
         </is>
       </c>
       <c r="B45" s="14" t="inlineStr">
         <is>
-          <t>어린이 안전 배움터 - 여름철 안전(물놀이)</t>
+          <t>학교폭력 &gt; 학교폭력 신고 및 초기대응 &gt; 학교폭력의 신고 및 고발</t>
         </is>
       </c>
       <c r="C45" s="13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D45" s="14" t="inlineStr">
         <is>
-          <t>안전</t>
+          <t>학교폭력</t>
         </is>
       </c>
       <c r="E45" s="15" t="inlineStr">
         <is>
-          <t>https://www.mois.go.kr/chd/sub/a06/summer/screen.do</t>
+          <t>https://easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=1408&amp;ccfNo=3&amp;cciNo=1&amp;cnpClsNo=1</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>법제처(찾기쉬운 생활법령정보)</t>
+          <t>한국환경보전원 탄소중립 정책포털</t>
         </is>
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>학교폭력 &gt; 학교폭력 신고 및 초기대응 &gt; 학교폭력의 신고 및 고발</t>
+          <t>기후변화 - 온실가스와 온실효과</t>
         </is>
       </c>
       <c r="C46" s="6" t="n">
@@ -29021,24 +29021,24 @@
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>학교폭력</t>
+          <t>환경</t>
         </is>
       </c>
       <c r="E46" s="12" t="inlineStr">
         <is>
-          <t>https://easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=1408&amp;ccfNo=3&amp;cciNo=1&amp;cnpClsNo=1</t>
+          <t>https://www.gihoo.or.kr/menu.es?mid=a30101010000</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="14" t="inlineStr">
         <is>
-          <t>한국환경보전원 탄소중립 정책포털</t>
+          <t>행정안전부</t>
         </is>
       </c>
       <c r="B47" s="14" t="inlineStr">
         <is>
-          <t>기후변화 - 온실가스와 온실효과</t>
+          <t>어린이 안전 배움터 - 도로·교통(어린이보호구역 교통안전수칙)</t>
         </is>
       </c>
       <c r="C47" s="13" t="n">
@@ -29046,49 +29046,49 @@
       </c>
       <c r="D47" s="14" t="inlineStr">
         <is>
-          <t>환경</t>
+          <t>안전</t>
         </is>
       </c>
       <c r="E47" s="15" t="inlineStr">
         <is>
-          <t>https://www.gihoo.or.kr/menu.es?mid=a30101010000</t>
+          <t>https://www.mois.go.kr/chd/sub/a06/road/screen.do</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>행정안전부</t>
+          <t>대한민국 정책브리핑(문화체육관광부 운영)</t>
         </is>
       </c>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>어린이 안전 배움터 - 도로·교통(어린이보호구역 교통안전수칙)</t>
+          <t>여름철 전기절약 행동요령</t>
         </is>
       </c>
       <c r="C48" s="6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>안전</t>
+          <t>환경</t>
         </is>
       </c>
       <c r="E48" s="12" t="inlineStr">
         <is>
-          <t>https://www.mois.go.kr/chd/sub/a06/road/screen.do</t>
+          <t>https://www.korea.kr/news/policyNewsView.do?newsId=148736371</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="14" t="inlineStr">
         <is>
-          <t>대한민국 정책브리핑(문화체육관광부 운영)</t>
+          <t>법제처(찾기쉬운 생활법령정보)</t>
         </is>
       </c>
       <c r="B49" s="14" t="inlineStr">
         <is>
-          <t>여름철 전기절약 행동요령</t>
+          <t>학교폭력 &gt; 학교폭력의 이해 &gt; 학교폭력의 개념 (학교폭력예방 및 대책에 관한 법률 제2조제1호의2)</t>
         </is>
       </c>
       <c r="C49" s="13" t="n">
@@ -29096,12 +29096,12 @@
       </c>
       <c r="D49" s="14" t="inlineStr">
         <is>
-          <t>환경</t>
+          <t>학교폭력</t>
         </is>
       </c>
       <c r="E49" s="15" t="inlineStr">
         <is>
-          <t>https://www.korea.kr/news/policyNewsView.do?newsId=148736371</t>
+          <t>https://www.easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=1408&amp;ccfNo=1&amp;cciNo=1&amp;cnpClsNo=1</t>
         </is>
       </c>
     </row>
@@ -29113,7 +29113,7 @@
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>학교폭력 &gt; 학교폭력의 이해 &gt; 학교폭력의 개념 (학교폭력예방 및 대책에 관한 법률 제2조제1호의2)</t>
+          <t>학교폭력 &gt; 학교폭력의 해결 &gt; 피해학생에 대한 보호 조치 (학교폭력예방 및 대책에 관한 법률 제16조)</t>
         </is>
       </c>
       <c r="C50" s="6" t="n">
@@ -29126,19 +29126,19 @@
       </c>
       <c r="E50" s="12" t="inlineStr">
         <is>
-          <t>https://www.easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=1408&amp;ccfNo=1&amp;cciNo=1&amp;cnpClsNo=1</t>
+          <t>https://easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=1408&amp;ccfNo=4&amp;cciNo=2&amp;cnpClsNo=3</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="14" t="inlineStr">
         <is>
-          <t>법제처(찾기쉬운 생활법령정보)</t>
+          <t>한국에너지공단</t>
         </is>
       </c>
       <c r="B51" s="14" t="inlineStr">
         <is>
-          <t>학교폭력 &gt; 학교폭력의 해결 &gt; 피해학생에 대한 보호 조치 (학교폭력예방 및 대책에 관한 법률 제16조)</t>
+          <t>보도자료 - 일상 속 작은 실천이 난방비 절약의 핵심(2025.2.28.)</t>
         </is>
       </c>
       <c r="C51" s="13" t="n">
@@ -29146,49 +29146,49 @@
       </c>
       <c r="D51" s="14" t="inlineStr">
         <is>
-          <t>학교폭력</t>
+          <t>환경</t>
         </is>
       </c>
       <c r="E51" s="15" t="inlineStr">
         <is>
-          <t>https://easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=1408&amp;ccfNo=4&amp;cciNo=2&amp;cnpClsNo=3</t>
+          <t>https://www.energy.or.kr/front/board/View3.do?boardMngNo=3&amp;boardNo=10024875</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t>한국에너지공단</t>
+          <t>교육부(위(Wee) 프로젝트)</t>
         </is>
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>보도자료 - 일상 속 작은 실천이 난방비 절약의 핵심(2025.2.28.)</t>
+          <t>위(Wee) 프로젝트 소개</t>
         </is>
       </c>
       <c r="C52" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>환경</t>
+          <t>학교폭력</t>
         </is>
       </c>
       <c r="E52" s="12" t="inlineStr">
         <is>
-          <t>https://www.energy.or.kr/front/board/View3.do?boardMngNo=3&amp;boardNo=10024875</t>
+          <t>https://www.wee.go.kr/menu?menuKey=eE85uGkNYN</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="14" t="inlineStr">
         <is>
-          <t>교육부(위(Wee) 프로젝트)</t>
+          <t>기상청</t>
         </is>
       </c>
       <c r="B53" s="14" t="inlineStr">
         <is>
-          <t>위(Wee) 프로젝트 소개</t>
+          <t>어린이 기상교실 - 지구온난화</t>
         </is>
       </c>
       <c r="C53" s="13" t="n">
@@ -29196,24 +29196,24 @@
       </c>
       <c r="D53" s="14" t="inlineStr">
         <is>
-          <t>학교폭력</t>
+          <t>환경</t>
         </is>
       </c>
       <c r="E53" s="15" t="inlineStr">
         <is>
-          <t>https://www.wee.go.kr/menu?menuKey=eE85uGkNYN</t>
+          <t>https://www.kma.go.kr/kids/231.jsp</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t>기상청</t>
+          <t>대한민국 정책브리핑(문화체육관광부 운영)</t>
         </is>
       </c>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>어린이 기상교실 - 지구온난화</t>
+          <t>[Q&amp;A] 투명 페트병, 어떻게 분리배출해야 하나</t>
         </is>
       </c>
       <c r="C54" s="6" t="n">
@@ -29226,19 +29226,19 @@
       </c>
       <c r="E54" s="12" t="inlineStr">
         <is>
-          <t>https://www.kma.go.kr/kids/231.jsp</t>
+          <t>https://www.korea.kr/news/policyNewsView.do?newsId=148881706</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="14" t="inlineStr">
         <is>
-          <t>대한민국 정책브리핑(문화체육관광부 운영)</t>
+          <t>법제처(찾기쉬운 생활법령정보)</t>
         </is>
       </c>
       <c r="B55" s="14" t="inlineStr">
         <is>
-          <t>[Q&amp;A] 투명 페트병, 어떻게 분리배출해야 하나</t>
+          <t>찾기쉬운 생활법령정보 - 화재예방을 위한 안전수칙</t>
         </is>
       </c>
       <c r="C55" s="13" t="n">
@@ -29246,24 +29246,24 @@
       </c>
       <c r="D55" s="14" t="inlineStr">
         <is>
-          <t>환경</t>
+          <t>안전</t>
         </is>
       </c>
       <c r="E55" s="15" t="inlineStr">
         <is>
-          <t>https://www.korea.kr/news/policyNewsView.do?newsId=148881706</t>
+          <t>https://easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=690&amp;ccfNo=5&amp;cciNo=1&amp;cnpClsNo=1</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t>질병관리청</t>
+          <t>법제처(찾기쉬운 생활법령정보)</t>
         </is>
       </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>국가건강정보포털 - 화상</t>
+          <t>찾기쉬운 생활법령정보 - 화재예방을 위한 안전수칙(화상 응급처치)</t>
         </is>
       </c>
       <c r="C56" s="6" t="n">
@@ -29276,7 +29276,7 @@
       </c>
       <c r="E56" s="12" t="inlineStr">
         <is>
-          <t>https://health.kdca.go.kr/healthinfo/biz/health/gnrlzHealthInfo/gnrlzHealthInfo/gnrlzHealthInfoView.do?cntnts_sn=6584</t>
+          <t>https://easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=690&amp;ccfNo=5&amp;cciNo=1&amp;cnpClsNo=1</t>
         </is>
       </c>
     </row>
@@ -29508,12 +29508,12 @@
     <row r="66">
       <c r="A66" s="7" t="inlineStr">
         <is>
-          <t>한국에너지공단</t>
+          <t>질병관리청</t>
         </is>
       </c>
       <c r="B66" s="7" t="inlineStr">
         <is>
-          <t>효율관리제도 - 에너지소비효율등급 표시제도 개요</t>
+          <t>국가건강정보포털 - 화상</t>
         </is>
       </c>
       <c r="C66" s="6" t="n">
@@ -29521,37 +29521,37 @@
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>환경</t>
+          <t>안전</t>
         </is>
       </c>
       <c r="E66" s="12" t="inlineStr">
         <is>
-          <t>https://eep.energy.or.kr/business_introduction/effi_summary.aspx</t>
+          <t>https://health.kdca.go.kr/healthinfo/biz/health/gnrlzHealthInfo/gnrlzHealthInfo/gnrlzHealthInfoView.do?cntnts_sn=6584</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="14" t="inlineStr">
         <is>
-          <t>교육부</t>
+          <t>한국에너지공단</t>
         </is>
       </c>
       <c r="B67" s="14" t="inlineStr">
         <is>
-          <t>학교 디지털 성폭력 초기 대응을 위한 '디지털 성폭력 에스오에스(SOS) 가이드' 발간(보도자료, 2025.4.22.)</t>
+          <t>효율관리제도 - 에너지소비효율등급 표시제도 개요</t>
         </is>
       </c>
       <c r="C67" s="13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D67" s="14" t="inlineStr">
         <is>
-          <t>학교폭력</t>
+          <t>환경</t>
         </is>
       </c>
       <c r="E67" s="15" t="inlineStr">
         <is>
-          <t>https://www.moe.go.kr/boardCnts/viewRenew.do?boardID=294&amp;boardSeq=103170&amp;lev=0&amp;statusYN=W&amp;s=moe&amp;m=020402&amp;opType=N</t>
+          <t>https://eep.energy.or.kr/business_introduction/effi_summary.aspx</t>
         </is>
       </c>
     </row>
@@ -29563,7 +29563,7 @@
       </c>
       <c r="B68" s="7" t="inlineStr">
         <is>
-          <t>학교폭력 예방교육! 공감과 소통의 '어울림 프로그램'과 함께해요 (보도자료, 2019.1.30.)</t>
+          <t>학교 디지털 성폭력 초기 대응을 위한 '디지털 성폭력 에스오에스(SOS) 가이드' 발간(보도자료, 2025.4.22.)</t>
         </is>
       </c>
       <c r="C68" s="6" t="n">
@@ -29576,19 +29576,19 @@
       </c>
       <c r="E68" s="12" t="inlineStr">
         <is>
-          <t>https://www.moe.go.kr/boardCnts/view.do?boardID=294&amp;boardSeq=76637&amp;lev=0&amp;statusYN=W&amp;s=moe&amp;m=020402&amp;opType=N</t>
+          <t>https://www.moe.go.kr/boardCnts/viewRenew.do?boardID=294&amp;boardSeq=103170&amp;lev=0&amp;statusYN=W&amp;s=moe&amp;m=020402&amp;opType=N</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="14" t="inlineStr">
         <is>
-          <t>기상청</t>
+          <t>교육부</t>
         </is>
       </c>
       <c r="B69" s="14" t="inlineStr">
         <is>
-          <t>보도자료 - 2025년 우리나라 이산화탄소 농도, 또 최고치 경신</t>
+          <t>학교폭력 예방교육! 공감과 소통의 '어울림 프로그램'과 함께해요 (보도자료, 2019.1.30.)</t>
         </is>
       </c>
       <c r="C69" s="13" t="n">
@@ -29596,24 +29596,24 @@
       </c>
       <c r="D69" s="14" t="inlineStr">
         <is>
-          <t>환경</t>
+          <t>학교폭력</t>
         </is>
       </c>
       <c r="E69" s="15" t="inlineStr">
         <is>
-          <t>https://www.kma.go.kr/kma/news/press_01.jsp?mode=view&amp;num=1194641</t>
+          <t>https://www.moe.go.kr/boardCnts/view.do?boardID=294&amp;boardSeq=76637&amp;lev=0&amp;statusYN=W&amp;s=moe&amp;m=020402&amp;opType=N</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="inlineStr">
         <is>
-          <t>대한민국 정책브리핑(문화체육관광부 운영)</t>
+          <t>기상청</t>
         </is>
       </c>
       <c r="B70" s="7" t="inlineStr">
         <is>
-          <t>새 학기, 자녀와 함께 교통안전수칙 알아봤습니다! (횡단보도 5원칙)</t>
+          <t>보도자료 - 2025년 우리나라 이산화탄소 농도, 또 최고치 경신</t>
         </is>
       </c>
       <c r="C70" s="6" t="n">
@@ -29621,24 +29621,24 @@
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>안전</t>
+          <t>환경</t>
         </is>
       </c>
       <c r="E70" s="12" t="inlineStr">
         <is>
-          <t>https://www.korea.kr/news/policyNewsView.do?newsId=148926855</t>
+          <t>https://www.kma.go.kr/kma/news/press_01.jsp?mode=view&amp;num=1194641</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="14" t="inlineStr">
         <is>
-          <t>법제처(찾기쉬운 생활법령정보)</t>
+          <t>대한민국 정책브리핑(문화체육관광부 운영)</t>
         </is>
       </c>
       <c r="B71" s="14" t="inlineStr">
         <is>
-          <t>찾기쉬운 생활법령정보 - 어린이통학버스의 안전설비</t>
+          <t>새 학기, 자녀와 함께 교통안전수칙 알아봤습니다! (횡단보도 5원칙)</t>
         </is>
       </c>
       <c r="C71" s="13" t="n">
@@ -29651,7 +29651,7 @@
       </c>
       <c r="E71" s="15" t="inlineStr">
         <is>
-          <t>https://easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=690&amp;ccfNo=1&amp;cciNo=2&amp;cnpClsNo=2</t>
+          <t>https://www.korea.kr/news/policyNewsView.do?newsId=148926855</t>
         </is>
       </c>
     </row>
@@ -29663,7 +29663,7 @@
       </c>
       <c r="B72" s="7" t="inlineStr">
         <is>
-          <t>학교폭력 &gt; 학교폭력의 해결 &gt; 가해학생에 대한 조치 (학교폭력예방 및 대책에 관한 법률 제17조)</t>
+          <t>찾기쉬운 생활법령정보 - 어린이통학버스의 안전설비</t>
         </is>
       </c>
       <c r="C72" s="6" t="n">
@@ -29671,12 +29671,12 @@
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>학교폭력</t>
+          <t>안전</t>
         </is>
       </c>
       <c r="E72" s="12" t="inlineStr">
         <is>
-          <t>https://easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=1408&amp;ccfNo=4&amp;cciNo=2&amp;cnpClsNo=6</t>
+          <t>https://easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=690&amp;ccfNo=1&amp;cciNo=2&amp;cnpClsNo=2</t>
         </is>
       </c>
     </row>
@@ -29688,7 +29688,7 @@
       </c>
       <c r="B73" s="14" t="inlineStr">
         <is>
-          <t>청소년의 인터넷 이용하기 &gt; 댓글을 다는 경우 &gt; 인터넷 명예훼손에 대처하는 방법 (정보통신망법 제70조제1항)</t>
+          <t>학교폭력 &gt; 학교폭력의 해결 &gt; 가해학생에 대한 조치 (학교폭력예방 및 대책에 관한 법률 제17조)</t>
         </is>
       </c>
       <c r="C73" s="13" t="n">
@@ -29701,7 +29701,7 @@
       </c>
       <c r="E73" s="15" t="inlineStr">
         <is>
-          <t>https://easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=659&amp;ccfNo=6&amp;cciNo=2&amp;cnpClsNo=1</t>
+          <t>https://easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=1408&amp;ccfNo=4&amp;cciNo=2&amp;cnpClsNo=6</t>
         </is>
       </c>
     </row>
@@ -29713,7 +29713,7 @@
       </c>
       <c r="B74" s="7" t="inlineStr">
         <is>
-          <t>학교폭력 &gt; 학교폭력 신고 및 초기대응 &gt; 학교폭력의 신고 및 고발 (학교폭력예방 및 대책에 관한 법률 제20조제5항)</t>
+          <t>청소년의 인터넷 이용하기 &gt; 댓글을 다는 경우 &gt; 인터넷 명예훼손에 대처하는 방법 (정보통신망법 제70조제1항)</t>
         </is>
       </c>
       <c r="C74" s="6" t="n">
@@ -29726,19 +29726,19 @@
       </c>
       <c r="E74" s="12" t="inlineStr">
         <is>
-          <t>https://easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=1408&amp;ccfNo=3&amp;cciNo=1&amp;cnpClsNo=1</t>
+          <t>https://easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=659&amp;ccfNo=6&amp;cciNo=2&amp;cnpClsNo=1</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="14" t="inlineStr">
         <is>
-          <t>행정안전부</t>
+          <t>법제처(찾기쉬운 생활법령정보)</t>
         </is>
       </c>
       <c r="B75" s="14" t="inlineStr">
         <is>
-          <t>어린이 안전 배움터 - 구조·구급(119 구급신고요령)</t>
+          <t>학교폭력 &gt; 학교폭력 신고 및 초기대응 &gt; 학교폭력의 신고 및 고발 (학교폭력예방 및 대책에 관한 법률 제20조제5항)</t>
         </is>
       </c>
       <c r="C75" s="13" t="n">
@@ -29746,49 +29746,49 @@
       </c>
       <c r="D75" s="14" t="inlineStr">
         <is>
-          <t>안전</t>
+          <t>학교폭력</t>
         </is>
       </c>
       <c r="E75" s="15" t="inlineStr">
         <is>
-          <t>https://www.mois.go.kr/chd/sub/a06/rescue/screen.do</t>
+          <t>https://easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=1408&amp;ccfNo=3&amp;cciNo=1&amp;cnpClsNo=1</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="7" t="inlineStr">
         <is>
-          <t>기상청</t>
+          <t>행정안전부</t>
         </is>
       </c>
       <c r="B76" s="7" t="inlineStr">
         <is>
-          <t>보도자료 - 2025년, 다양한 이상기후로 확인된 '기후위기의 시대'</t>
+          <t>어린이 안전 배움터 - 구조·구급(119 구급신고요령)</t>
         </is>
       </c>
       <c r="C76" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>환경</t>
+          <t>안전</t>
         </is>
       </c>
       <c r="E76" s="12" t="inlineStr">
         <is>
-          <t>https://www.kma.go.kr/kma/news/press.jsp?bid=press&amp;mode=view&amp;num=1194622</t>
+          <t>https://www.mois.go.kr/chd/sub/a06/rescue/screen.do</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="14" t="inlineStr">
         <is>
-          <t>법제처(찾기쉬운 생활법령정보)</t>
+          <t>기상청</t>
         </is>
       </c>
       <c r="B77" s="14" t="inlineStr">
         <is>
-          <t>찾기쉬운 생활법령정보 - 어린이 보행사고 예방을 위한 안전수칙(도로교통법 제10조제2항)</t>
+          <t>보도자료 - 2025년, 다양한 이상기후로 확인된 '기후위기의 시대'</t>
         </is>
       </c>
       <c r="C77" s="13" t="n">
@@ -29796,12 +29796,12 @@
       </c>
       <c r="D77" s="14" t="inlineStr">
         <is>
-          <t>안전</t>
+          <t>환경</t>
         </is>
       </c>
       <c r="E77" s="15" t="inlineStr">
         <is>
-          <t>https://www.easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=690&amp;ccfNo=1&amp;cciNo=1&amp;cnpClsNo=1</t>
+          <t>https://www.kma.go.kr/kma/news/press.jsp?bid=press&amp;mode=view&amp;num=1194622</t>
         </is>
       </c>
     </row>
@@ -29813,7 +29813,7 @@
       </c>
       <c r="B78" s="7" t="inlineStr">
         <is>
-          <t>찾기쉬운 생활법령정보 - 어린이 자전거 안전(도로교통법 제11조제3항)</t>
+          <t>찾기쉬운 생활법령정보 - 어린이 보행사고 예방을 위한 안전수칙(도로교통법 제10조제2항)</t>
         </is>
       </c>
       <c r="C78" s="6" t="n">
@@ -29826,7 +29826,7 @@
       </c>
       <c r="E78" s="12" t="inlineStr">
         <is>
-          <t>https://www.easylaw.go.kr/CSP/CnpClsMainBtr.laf?popMenu=ov&amp;csmSeq=690&amp;ccfNo=1&amp;cciNo=3&amp;cnpClsNo=1</t>
+          <t>https://www.easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=690&amp;ccfNo=1&amp;cciNo=1&amp;cnpClsNo=1</t>
         </is>
       </c>
     </row>
@@ -29838,7 +29838,7 @@
       </c>
       <c r="B79" s="14" t="inlineStr">
         <is>
-          <t>찾기쉬운 생활법령정보 - 어린이 자전거 안전(도로교통법 제13조의2제6항)</t>
+          <t>찾기쉬운 생활법령정보 - 어린이 자전거 안전(도로교통법 제11조제3항)</t>
         </is>
       </c>
       <c r="C79" s="13" t="n">
@@ -29863,7 +29863,7 @@
       </c>
       <c r="B80" s="7" t="inlineStr">
         <is>
-          <t>찾기쉬운 생활법령정보 - 어린이 생활안전(어린이 보호구역)</t>
+          <t>찾기쉬운 생활법령정보 - 어린이 자전거 안전(도로교통법 제13조의2제6항)</t>
         </is>
       </c>
       <c r="C80" s="6" t="n">
@@ -29876,7 +29876,7 @@
       </c>
       <c r="E80" s="12" t="inlineStr">
         <is>
-          <t>https://www.easylaw.go.kr/CSP/CnpClsMainBtr.laf?popMenu=ov&amp;csmSeq=690&amp;ccfNo=1&amp;cciNo=1&amp;cnpClsNo=3</t>
+          <t>https://www.easylaw.go.kr/CSP/CnpClsMainBtr.laf?popMenu=ov&amp;csmSeq=690&amp;ccfNo=1&amp;cciNo=3&amp;cnpClsNo=1</t>
         </is>
       </c>
     </row>
@@ -29888,7 +29888,7 @@
       </c>
       <c r="B81" s="14" t="inlineStr">
         <is>
-          <t>찾기쉬운 생활법령정보 - 가정의 차량 탑승 시 안전수칙(도로교통법 제50조제1항)</t>
+          <t>찾기쉬운 생활법령정보 - 어린이 생활안전(어린이 보호구역)</t>
         </is>
       </c>
       <c r="C81" s="13" t="n">
@@ -29901,7 +29901,7 @@
       </c>
       <c r="E81" s="15" t="inlineStr">
         <is>
-          <t>https://easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=690&amp;ccfNo=1&amp;cciNo=2&amp;cnpClsNo=1</t>
+          <t>https://www.easylaw.go.kr/CSP/CnpClsMainBtr.laf?popMenu=ov&amp;csmSeq=690&amp;ccfNo=1&amp;cciNo=1&amp;cnpClsNo=3</t>
         </is>
       </c>
     </row>
@@ -29913,7 +29913,7 @@
       </c>
       <c r="B82" s="7" t="inlineStr">
         <is>
-          <t>찾기쉬운 생활법령정보 - 가정의 차량 탑승 시 안전수칙(도로교통법 제49조제1항제7호)</t>
+          <t>찾기쉬운 생활법령정보 - 가정의 차량 탑승 시 안전수칙(도로교통법 제50조제1항)</t>
         </is>
       </c>
       <c r="C82" s="6" t="n">
@@ -29938,7 +29938,7 @@
       </c>
       <c r="B83" s="14" t="inlineStr">
         <is>
-          <t>찾기쉬운 생활법령정보 - 화재예방을 위한 안전수칙(화상 응급처치)</t>
+          <t>찾기쉬운 생활법령정보 - 가정의 차량 탑승 시 안전수칙(도로교통법 제49조제1항제7호)</t>
         </is>
       </c>
       <c r="C83" s="13" t="n">
@@ -29951,7 +29951,7 @@
       </c>
       <c r="E83" s="15" t="inlineStr">
         <is>
-          <t>https://easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=690&amp;ccfNo=5&amp;cciNo=1&amp;cnpClsNo=1</t>
+          <t>https://easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=690&amp;ccfNo=1&amp;cciNo=2&amp;cnpClsNo=1</t>
         </is>
       </c>
     </row>
@@ -30183,37 +30183,37 @@
     <row r="93">
       <c r="A93" s="14" t="inlineStr">
         <is>
-          <t>교육부</t>
+          <t>행정안전부</t>
         </is>
       </c>
       <c r="B93" s="14" t="inlineStr">
         <is>
-          <t>초1·2 학폭 심의 전 '관계회복 프로그램' 우선 실시 (정책브리핑, 2025.4.30.)</t>
+          <t>국민안전24 - 전기·가스 사고 국민행동요령</t>
         </is>
       </c>
       <c r="C93" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D93" s="14" t="inlineStr">
         <is>
-          <t>학교폭력</t>
+          <t>안전</t>
         </is>
       </c>
       <c r="E93" s="15" t="inlineStr">
         <is>
-          <t>https://www.korea.kr/news/policyNewsView.do?newsId=148942634</t>
+          <t>https://www.safekorea.go.kr/safekorea-kor/acts/nacts/action-guide.do?category=electircGasAccident&amp;actsHeaderTitle=%EC%A0%84%EA%B8%B0%C2%B7%EA%B0%80%EC%8A%A4+%EC%82%AC%EA%B3%A0&amp;menuSn=4</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="7" t="inlineStr">
         <is>
-          <t>대한민국 정책브리핑(문화체육관광부 운영)</t>
+          <t>교육부</t>
         </is>
       </c>
       <c r="B94" s="7" t="inlineStr">
         <is>
-          <t>어린이 교통안전 수칙을 지켜라</t>
+          <t>초1·2 학폭 심의 전 '관계회복 프로그램' 우선 실시 (정책브리핑, 2025.4.30.)</t>
         </is>
       </c>
       <c r="C94" s="6" t="n">
@@ -30221,24 +30221,24 @@
       </c>
       <c r="D94" s="7" t="inlineStr">
         <is>
-          <t>안전</t>
+          <t>학교폭력</t>
         </is>
       </c>
       <c r="E94" s="12" t="inlineStr">
         <is>
-          <t>https://www.korea.kr/news/policyNewsView.do?newsId=148954485</t>
+          <t>https://www.korea.kr/news/policyNewsView.do?newsId=148942634</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="14" t="inlineStr">
         <is>
-          <t>법제처(찾기쉬운 생활법령정보)</t>
+          <t>대한민국 정책브리핑(문화체육관광부 운영)</t>
         </is>
       </c>
       <c r="B95" s="14" t="inlineStr">
         <is>
-          <t>찾기쉬운 생활법령정보 - 어린이 자전거 안전(도로교통법 제13조의2제2항)</t>
+          <t>어린이 교통안전 수칙을 지켜라</t>
         </is>
       </c>
       <c r="C95" s="13" t="n">
@@ -30251,7 +30251,7 @@
       </c>
       <c r="E95" s="15" t="inlineStr">
         <is>
-          <t>https://www.easylaw.go.kr/CSP/CnpClsMainBtr.laf?popMenu=ov&amp;csmSeq=690&amp;ccfNo=1&amp;cciNo=3&amp;cnpClsNo=1</t>
+          <t>https://www.korea.kr/news/policyNewsView.do?newsId=148954485</t>
         </is>
       </c>
     </row>
@@ -30263,7 +30263,7 @@
       </c>
       <c r="B96" s="7" t="inlineStr">
         <is>
-          <t>학교폭력 &gt; 학교폭력의 이해 &gt; 학교폭력의 개념 (학교폭력예방 및 대책에 관한 법률 제2조)</t>
+          <t>찾기쉬운 생활법령정보 - 어린이 자전거 안전(도로교통법 제13조의2제2항)</t>
         </is>
       </c>
       <c r="C96" s="6" t="n">
@@ -30271,10 +30271,35 @@
       </c>
       <c r="D96" s="7" t="inlineStr">
         <is>
+          <t>안전</t>
+        </is>
+      </c>
+      <c r="E96" s="12" t="inlineStr">
+        <is>
+          <t>https://www.easylaw.go.kr/CSP/CnpClsMainBtr.laf?popMenu=ov&amp;csmSeq=690&amp;ccfNo=1&amp;cciNo=3&amp;cnpClsNo=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="14" t="inlineStr">
+        <is>
+          <t>법제처(찾기쉬운 생활법령정보)</t>
+        </is>
+      </c>
+      <c r="B97" s="14" t="inlineStr">
+        <is>
+          <t>학교폭력 &gt; 학교폭력의 이해 &gt; 학교폭력의 개념 (학교폭력예방 및 대책에 관한 법률 제2조)</t>
+        </is>
+      </c>
+      <c r="C97" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D97" s="14" t="inlineStr">
+        <is>
           <t>학교폭력</t>
         </is>
       </c>
-      <c r="E96" s="12" t="inlineStr">
+      <c r="E97" s="15" t="inlineStr">
         <is>
           <t>https://www.easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=1408&amp;ccfNo=1&amp;cciNo=1&amp;cnpClsNo=1</t>
         </is>
@@ -30353,6 +30378,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E94" r:id="rId69"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E95" r:id="rId70"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E96" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E97" r:id="rId72"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/quiz/수업도우미_퀴즈_문항과출처.xlsx
+++ b/quiz/수업도우미_퀴즈_문항과출처.xlsx
@@ -10775,7 +10775,7 @@
       </c>
       <c r="B95" s="7" t="inlineStr">
         <is>
-          <t>자전거를 탈 때 두 손을 놓고 타도 실력만 좋으면 괜찮아요.</t>
+          <t>자전거를 탈 때 헤드폰이나 이어폰을 끼고 타도 괜찮아요.</t>
         </is>
       </c>
       <c r="C95" s="6" t="inlineStr">
@@ -10785,7 +10785,7 @@
       </c>
       <c r="D95" s="7" t="inlineStr">
         <is>
-          <t>틀려요! 두 손을 놓으면 갑자기 멈추거나 피할 수 없어 위험해요.</t>
+          <t>틀려요! 주행 중에는 헤드폰·이어폰을 쓰지 않아야 해요.</t>
         </is>
       </c>
       <c r="E95" s="7" t="inlineStr">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="G95" s="7" t="inlineStr">
         <is>
-          <t>찾기쉬운 생활법령정보 - 어린이 자전거 안전(도로교통법 제11조제3항)</t>
+          <t>찾기쉬운 생활법령정보 - 어린이 자전거 안전</t>
         </is>
       </c>
       <c r="H95" s="12" t="inlineStr">
@@ -10825,7 +10825,7 @@
       </c>
       <c r="D96" s="14" t="inlineStr">
         <is>
-          <t>틀려요! 전조등과 미등을 켜야 다른 사람 눈에 잘 띄어요.</t>
+          <t>틀려요! 야간 운행에는 라이트를 켜야 해요.</t>
         </is>
       </c>
       <c r="E96" s="14" t="inlineStr">
@@ -10835,17 +10835,17 @@
       </c>
       <c r="F96" s="14" t="inlineStr">
         <is>
-          <t>법제처(찾기쉬운 생활법령정보)</t>
+          <t>행정안전부</t>
         </is>
       </c>
       <c r="G96" s="14" t="inlineStr">
         <is>
-          <t>찾기쉬운 생활법령정보 - 어린이 자전거 안전(도로교통법 제13조의2제6항)</t>
+          <t>어린이 안전 배움터 - 자전거 안전(놀이기구)</t>
         </is>
       </c>
       <c r="H96" s="15" t="inlineStr">
         <is>
-          <t>https://www.easylaw.go.kr/CSP/CnpClsMainBtr.laf?popMenu=ov&amp;csmSeq=690&amp;ccfNo=1&amp;cciNo=3&amp;cnpClsNo=1</t>
+          <t>https://www.mois.go.kr/chd/sub/a06/play/screen.do</t>
         </is>
       </c>
     </row>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="H71" s="12" t="inlineStr">
         <is>
-          <t>https://www.easylaw.go.kr/CSP/CnpClsMainBtr.laf?popMenu=ov&amp;csmSeq=1408&amp;ccfNo=4&amp;cciNo=1&amp;cnpClsNo=1</t>
+          <t>https://www.easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=1408&amp;ccfNo=4&amp;cciNo=1&amp;cnpClsNo=1</t>
         </is>
       </c>
     </row>
@@ -18999,7 +18999,7 @@
       </c>
       <c r="H143" s="12" t="inlineStr">
         <is>
-          <t>https://www.easylaw.go.kr/CSP/CnpClsMainBtr.laf?popMenu=ov&amp;csmSeq=1408&amp;ccfNo=4&amp;cciNo=1&amp;cnpClsNo=1</t>
+          <t>https://www.easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=1408&amp;ccfNo=4&amp;cciNo=1&amp;cnpClsNo=1</t>
         </is>
       </c>
     </row>
@@ -19359,7 +19359,7 @@
       </c>
       <c r="H152" s="15" t="inlineStr">
         <is>
-          <t>https://www.easylaw.go.kr/CSP/CnpClsMainBtr.laf?popMenu=ov&amp;csmSeq=1408&amp;ccfNo=4&amp;cciNo=1&amp;cnpClsNo=1</t>
+          <t>https://www.easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=1408&amp;ccfNo=4&amp;cciNo=1&amp;cnpClsNo=1</t>
         </is>
       </c>
     </row>
@@ -19399,7 +19399,7 @@
       </c>
       <c r="H153" s="12" t="inlineStr">
         <is>
-          <t>https://www.easylaw.go.kr/CSP/CnpClsMainBtr.laf?popMenu=ov&amp;csmSeq=1408&amp;ccfNo=4&amp;cciNo=1&amp;cnpClsNo=1</t>
+          <t>https://www.easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=1408&amp;ccfNo=4&amp;cciNo=1&amp;cnpClsNo=1</t>
         </is>
       </c>
     </row>
@@ -28184,7 +28184,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E97"/>
+  <dimension ref="A1:E99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -28239,7 +28239,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C6" s="16">
         <f>B6/$B$22</f>
@@ -28249,11 +28249,11 @@
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>기후에너지환경부</t>
+          <t>행정안전부</t>
         </is>
       </c>
       <c r="B7" s="13" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C7" s="17">
         <f>B7/$B$22</f>
@@ -28263,7 +28263,7 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>행정안전부</t>
+          <t>기후에너지환경부</t>
         </is>
       </c>
       <c r="B8" s="6" t="n">
@@ -28474,7 +28474,7 @@
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t>문서별 (72종)</t>
+          <t>문서별 (74종)</t>
         </is>
       </c>
     </row>
@@ -29451,7 +29451,7 @@
       </c>
       <c r="E63" s="15" t="inlineStr">
         <is>
-          <t>https://www.easylaw.go.kr/CSP/CnpClsMainBtr.laf?popMenu=ov&amp;csmSeq=1408&amp;ccfNo=4&amp;cciNo=1&amp;cnpClsNo=1</t>
+          <t>https://www.easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=1408&amp;ccfNo=4&amp;cciNo=1&amp;cnpClsNo=1</t>
         </is>
       </c>
     </row>
@@ -29838,7 +29838,7 @@
       </c>
       <c r="B79" s="14" t="inlineStr">
         <is>
-          <t>찾기쉬운 생활법령정보 - 어린이 자전거 안전(도로교통법 제11조제3항)</t>
+          <t>찾기쉬운 생활법령정보 - 어린이 생활안전(어린이 보호구역)</t>
         </is>
       </c>
       <c r="C79" s="13" t="n">
@@ -29851,7 +29851,7 @@
       </c>
       <c r="E79" s="15" t="inlineStr">
         <is>
-          <t>https://www.easylaw.go.kr/CSP/CnpClsMainBtr.laf?popMenu=ov&amp;csmSeq=690&amp;ccfNo=1&amp;cciNo=3&amp;cnpClsNo=1</t>
+          <t>https://www.easylaw.go.kr/CSP/CnpClsMainBtr.laf?popMenu=ov&amp;csmSeq=690&amp;ccfNo=1&amp;cciNo=1&amp;cnpClsNo=3</t>
         </is>
       </c>
     </row>
@@ -29863,7 +29863,7 @@
       </c>
       <c r="B80" s="7" t="inlineStr">
         <is>
-          <t>찾기쉬운 생활법령정보 - 어린이 자전거 안전(도로교통법 제13조의2제6항)</t>
+          <t>찾기쉬운 생활법령정보 - 가정의 차량 탑승 시 안전수칙(도로교통법 제50조제1항)</t>
         </is>
       </c>
       <c r="C80" s="6" t="n">
@@ -29876,7 +29876,7 @@
       </c>
       <c r="E80" s="12" t="inlineStr">
         <is>
-          <t>https://www.easylaw.go.kr/CSP/CnpClsMainBtr.laf?popMenu=ov&amp;csmSeq=690&amp;ccfNo=1&amp;cciNo=3&amp;cnpClsNo=1</t>
+          <t>https://easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=690&amp;ccfNo=1&amp;cciNo=2&amp;cnpClsNo=1</t>
         </is>
       </c>
     </row>
@@ -29888,7 +29888,7 @@
       </c>
       <c r="B81" s="14" t="inlineStr">
         <is>
-          <t>찾기쉬운 생활법령정보 - 어린이 생활안전(어린이 보호구역)</t>
+          <t>찾기쉬운 생활법령정보 - 가정의 차량 탑승 시 안전수칙(도로교통법 제49조제1항제7호)</t>
         </is>
       </c>
       <c r="C81" s="13" t="n">
@@ -29901,7 +29901,7 @@
       </c>
       <c r="E81" s="15" t="inlineStr">
         <is>
-          <t>https://www.easylaw.go.kr/CSP/CnpClsMainBtr.laf?popMenu=ov&amp;csmSeq=690&amp;ccfNo=1&amp;cciNo=1&amp;cnpClsNo=3</t>
+          <t>https://easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=690&amp;ccfNo=1&amp;cciNo=2&amp;cnpClsNo=1</t>
         </is>
       </c>
     </row>
@@ -29913,7 +29913,7 @@
       </c>
       <c r="B82" s="7" t="inlineStr">
         <is>
-          <t>찾기쉬운 생활법령정보 - 가정의 차량 탑승 시 안전수칙(도로교통법 제50조제1항)</t>
+          <t>학교폭력 &gt; 사전예방 &gt; 학교폭력 예방교육 실시 (학교폭력예방 및 대책에 관한 법률 제15조)</t>
         </is>
       </c>
       <c r="C82" s="6" t="n">
@@ -29921,12 +29921,12 @@
       </c>
       <c r="D82" s="7" t="inlineStr">
         <is>
-          <t>안전</t>
+          <t>학교폭력</t>
         </is>
       </c>
       <c r="E82" s="12" t="inlineStr">
         <is>
-          <t>https://easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=690&amp;ccfNo=1&amp;cciNo=2&amp;cnpClsNo=1</t>
+          <t>https://www.easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=1408&amp;ccfNo=2&amp;cciNo=2&amp;cnpClsNo=1</t>
         </is>
       </c>
     </row>
@@ -29938,7 +29938,7 @@
       </c>
       <c r="B83" s="14" t="inlineStr">
         <is>
-          <t>찾기쉬운 생활법령정보 - 가정의 차량 탑승 시 안전수칙(도로교통법 제49조제1항제7호)</t>
+          <t>학교폭력 &gt; 학교폭력 신고 및 초기대응 &gt; 학교폭력의 신고 및 고발 (학교폭력예방 및 대책에 관한 법률 제20조)</t>
         </is>
       </c>
       <c r="C83" s="13" t="n">
@@ -29946,12 +29946,12 @@
       </c>
       <c r="D83" s="14" t="inlineStr">
         <is>
-          <t>안전</t>
+          <t>학교폭력</t>
         </is>
       </c>
       <c r="E83" s="15" t="inlineStr">
         <is>
-          <t>https://easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=690&amp;ccfNo=1&amp;cciNo=2&amp;cnpClsNo=1</t>
+          <t>https://easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=1408&amp;ccfNo=3&amp;cciNo=1&amp;cnpClsNo=1</t>
         </is>
       </c>
     </row>
@@ -29963,7 +29963,7 @@
       </c>
       <c r="B84" s="7" t="inlineStr">
         <is>
-          <t>학교폭력 &gt; 사전예방 &gt; 학교폭력 예방교육 실시 (학교폭력예방 및 대책에 관한 법률 제15조)</t>
+          <t>학교폭력 &gt; 학교폭력의 해결 &gt; 가해학생에 대한 조치 (학교폭력예방 및 대책에 관한 법률 제17조제1항제2호)</t>
         </is>
       </c>
       <c r="C84" s="6" t="n">
@@ -29976,7 +29976,7 @@
       </c>
       <c r="E84" s="12" t="inlineStr">
         <is>
-          <t>https://www.easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=1408&amp;ccfNo=2&amp;cciNo=2&amp;cnpClsNo=1</t>
+          <t>https://easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=1408&amp;ccfNo=4&amp;cciNo=2&amp;cnpClsNo=6</t>
         </is>
       </c>
     </row>
@@ -29988,7 +29988,7 @@
       </c>
       <c r="B85" s="14" t="inlineStr">
         <is>
-          <t>학교폭력 &gt; 학교폭력 신고 및 초기대응 &gt; 학교폭력의 신고 및 고발 (학교폭력예방 및 대책에 관한 법률 제20조)</t>
+          <t>학교폭력 &gt; 학교폭력 신고 및 초기대응 &gt; 학교폭력의 신고 및 고발 (학교폭력예방 및 대책에 관한 법률 제20조제4항)</t>
         </is>
       </c>
       <c r="C85" s="13" t="n">
@@ -30013,7 +30013,7 @@
       </c>
       <c r="B86" s="7" t="inlineStr">
         <is>
-          <t>학교폭력 &gt; 학교폭력의 해결 &gt; 가해학생에 대한 조치 (학교폭력예방 및 대책에 관한 법률 제17조제1항제2호)</t>
+          <t>학교폭력 &gt; 학교폭력 신고 및 초기대응 &gt; 학교폭력의 신고 및 고발 (학교폭력예방 및 대책에 관한 법률 제21조)</t>
         </is>
       </c>
       <c r="C86" s="6" t="n">
@@ -30026,7 +30026,7 @@
       </c>
       <c r="E86" s="12" t="inlineStr">
         <is>
-          <t>https://easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=1408&amp;ccfNo=4&amp;cciNo=2&amp;cnpClsNo=6</t>
+          <t>https://www.easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=1408&amp;ccfNo=3&amp;cciNo=1&amp;cnpClsNo=1&amp;menuType=onhunqna</t>
         </is>
       </c>
     </row>
@@ -30038,7 +30038,7 @@
       </c>
       <c r="B87" s="14" t="inlineStr">
         <is>
-          <t>학교폭력 &gt; 학교폭력 신고 및 초기대응 &gt; 학교폭력의 신고 및 고발 (학교폭력예방 및 대책에 관한 법률 제20조제4항)</t>
+          <t>학교폭력 &gt; 학교폭력의 해결 &gt; 가해학생에 대한 조치 (학교폭력예방 및 대책에 관한 법률 제17조제1항제1호)</t>
         </is>
       </c>
       <c r="C87" s="13" t="n">
@@ -30051,19 +30051,19 @@
       </c>
       <c r="E87" s="15" t="inlineStr">
         <is>
-          <t>https://easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=1408&amp;ccfNo=3&amp;cciNo=1&amp;cnpClsNo=1</t>
+          <t>https://easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=1408&amp;ccfNo=4&amp;cciNo=2&amp;cnpClsNo=6</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="7" t="inlineStr">
         <is>
-          <t>법제처(찾기쉬운 생활법령정보)</t>
+          <t>푸른나무재단</t>
         </is>
       </c>
       <c r="B88" s="7" t="inlineStr">
         <is>
-          <t>학교폭력 &gt; 학교폭력 신고 및 초기대응 &gt; 학교폭력의 신고 및 고발 (학교폭력예방 및 대책에 관한 법률 제21조)</t>
+          <t>푸른나무재단 청소년 전문 상담·지원 안내</t>
         </is>
       </c>
       <c r="C88" s="6" t="n">
@@ -30076,19 +30076,19 @@
       </c>
       <c r="E88" s="12" t="inlineStr">
         <is>
-          <t>https://www.easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=1408&amp;ccfNo=3&amp;cciNo=1&amp;cnpClsNo=1&amp;menuType=onhunqna</t>
+          <t>https://btf.or.kr/business/bus01.asp?scrID=0000000108&amp;pageNum=3&amp;subNum=1&amp;ssubNum=1</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="14" t="inlineStr">
         <is>
-          <t>법제처(찾기쉬운 생활법령정보)</t>
+          <t>한국환경보전원 탄소중립 정책포털</t>
         </is>
       </c>
       <c r="B89" s="14" t="inlineStr">
         <is>
-          <t>학교폭력 &gt; 학교폭력의 해결 &gt; 가해학생에 대한 조치 (학교폭력예방 및 대책에 관한 법률 제17조제1항제1호)</t>
+          <t>우리나라 기후변화</t>
         </is>
       </c>
       <c r="C89" s="13" t="n">
@@ -30096,24 +30096,24 @@
       </c>
       <c r="D89" s="14" t="inlineStr">
         <is>
-          <t>학교폭력</t>
+          <t>환경</t>
         </is>
       </c>
       <c r="E89" s="15" t="inlineStr">
         <is>
-          <t>https://easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=1408&amp;ccfNo=4&amp;cciNo=2&amp;cnpClsNo=6</t>
+          <t>https://www.gihoo.or.kr/menu.es?mid=a30101030000</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="7" t="inlineStr">
         <is>
-          <t>푸른나무재단</t>
+          <t>행정안전부</t>
         </is>
       </c>
       <c r="B90" s="7" t="inlineStr">
         <is>
-          <t>푸른나무재단 청소년 전문 상담·지원 안내</t>
+          <t>어린이 안전 배움터 - 구조·구급(심폐소생술)</t>
         </is>
       </c>
       <c r="C90" s="6" t="n">
@@ -30121,24 +30121,24 @@
       </c>
       <c r="D90" s="7" t="inlineStr">
         <is>
-          <t>학교폭력</t>
+          <t>안전</t>
         </is>
       </c>
       <c r="E90" s="12" t="inlineStr">
         <is>
-          <t>https://btf.or.kr/business/bus01.asp?scrID=0000000108&amp;pageNum=3&amp;subNum=1&amp;ssubNum=1</t>
+          <t>https://www.mois.go.kr/chd/sub/a06/rescue_3/screen.do</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="14" t="inlineStr">
         <is>
-          <t>한국환경보전원 탄소중립 정책포털</t>
+          <t>행정안전부</t>
         </is>
       </c>
       <c r="B91" s="14" t="inlineStr">
         <is>
-          <t>우리나라 기후변화</t>
+          <t>국민안전24 - 전기·가스 사고 국민행동요령</t>
         </is>
       </c>
       <c r="C91" s="13" t="n">
@@ -30146,53 +30146,53 @@
       </c>
       <c r="D91" s="14" t="inlineStr">
         <is>
-          <t>환경</t>
+          <t>안전</t>
         </is>
       </c>
       <c r="E91" s="15" t="inlineStr">
         <is>
-          <t>https://www.gihoo.or.kr/menu.es?mid=a30101030000</t>
+          <t>https://www.safekorea.go.kr/safekorea-kor/acts/nacts/action-guide.do?category=electircGasAccident&amp;actsHeaderTitle=%EC%A0%84%EA%B8%B0%C2%B7%EA%B0%80%EC%8A%A4+%EC%82%AC%EA%B3%A0&amp;menuSn=4</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="7" t="inlineStr">
         <is>
-          <t>행정안전부</t>
+          <t>교육부</t>
         </is>
       </c>
       <c r="B92" s="7" t="inlineStr">
         <is>
-          <t>어린이 안전 배움터 - 구조·구급(심폐소생술)</t>
+          <t>초1·2 학폭 심의 전 '관계회복 프로그램' 우선 실시 (정책브리핑, 2025.4.30.)</t>
         </is>
       </c>
       <c r="C92" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D92" s="7" t="inlineStr">
         <is>
-          <t>안전</t>
+          <t>학교폭력</t>
         </is>
       </c>
       <c r="E92" s="12" t="inlineStr">
         <is>
-          <t>https://www.mois.go.kr/chd/sub/a06/rescue_3/screen.do</t>
+          <t>https://www.korea.kr/news/policyNewsView.do?newsId=148942634</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="14" t="inlineStr">
         <is>
-          <t>행정안전부</t>
+          <t>대한민국 정책브리핑(문화체육관광부 운영)</t>
         </is>
       </c>
       <c r="B93" s="14" t="inlineStr">
         <is>
-          <t>국민안전24 - 전기·가스 사고 국민행동요령</t>
+          <t>어린이 교통안전 수칙을 지켜라</t>
         </is>
       </c>
       <c r="C93" s="13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D93" s="14" t="inlineStr">
         <is>
@@ -30201,19 +30201,19 @@
       </c>
       <c r="E93" s="15" t="inlineStr">
         <is>
-          <t>https://www.safekorea.go.kr/safekorea-kor/acts/nacts/action-guide.do?category=electircGasAccident&amp;actsHeaderTitle=%EC%A0%84%EA%B8%B0%C2%B7%EA%B0%80%EC%8A%A4+%EC%82%AC%EA%B3%A0&amp;menuSn=4</t>
+          <t>https://www.korea.kr/news/policyNewsView.do?newsId=148954485</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="7" t="inlineStr">
         <is>
-          <t>교육부</t>
+          <t>법제처(찾기쉬운 생활법령정보)</t>
         </is>
       </c>
       <c r="B94" s="7" t="inlineStr">
         <is>
-          <t>초1·2 학폭 심의 전 '관계회복 프로그램' 우선 실시 (정책브리핑, 2025.4.30.)</t>
+          <t>찾기쉬운 생활법령정보 - 어린이 자전거 안전(도로교통법 제11조제3항)</t>
         </is>
       </c>
       <c r="C94" s="6" t="n">
@@ -30221,24 +30221,24 @@
       </c>
       <c r="D94" s="7" t="inlineStr">
         <is>
-          <t>학교폭력</t>
+          <t>안전</t>
         </is>
       </c>
       <c r="E94" s="12" t="inlineStr">
         <is>
-          <t>https://www.korea.kr/news/policyNewsView.do?newsId=148942634</t>
+          <t>https://www.easylaw.go.kr/CSP/CnpClsMainBtr.laf?popMenu=ov&amp;csmSeq=690&amp;ccfNo=1&amp;cciNo=3&amp;cnpClsNo=1</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="14" t="inlineStr">
         <is>
-          <t>대한민국 정책브리핑(문화체육관광부 운영)</t>
+          <t>법제처(찾기쉬운 생활법령정보)</t>
         </is>
       </c>
       <c r="B95" s="14" t="inlineStr">
         <is>
-          <t>어린이 교통안전 수칙을 지켜라</t>
+          <t>찾기쉬운 생활법령정보 - 어린이 자전거 안전(도로교통법 제13조의2제6항)</t>
         </is>
       </c>
       <c r="C95" s="13" t="n">
@@ -30251,7 +30251,7 @@
       </c>
       <c r="E95" s="15" t="inlineStr">
         <is>
-          <t>https://www.korea.kr/news/policyNewsView.do?newsId=148954485</t>
+          <t>https://www.easylaw.go.kr/CSP/CnpClsMainBtr.laf?popMenu=ov&amp;csmSeq=690&amp;ccfNo=1&amp;cciNo=3&amp;cnpClsNo=1</t>
         </is>
       </c>
     </row>
@@ -30288,7 +30288,7 @@
       </c>
       <c r="B97" s="14" t="inlineStr">
         <is>
-          <t>학교폭력 &gt; 학교폭력의 이해 &gt; 학교폭력의 개념 (학교폭력예방 및 대책에 관한 법률 제2조)</t>
+          <t>찾기쉬운 생활법령정보 - 어린이 자전거 안전</t>
         </is>
       </c>
       <c r="C97" s="13" t="n">
@@ -30296,12 +30296,62 @@
       </c>
       <c r="D97" s="14" t="inlineStr">
         <is>
+          <t>안전</t>
+        </is>
+      </c>
+      <c r="E97" s="15" t="inlineStr">
+        <is>
+          <t>https://www.easylaw.go.kr/CSP/CnpClsMainBtr.laf?popMenu=ov&amp;csmSeq=690&amp;ccfNo=1&amp;cciNo=3&amp;cnpClsNo=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="7" t="inlineStr">
+        <is>
+          <t>법제처(찾기쉬운 생활법령정보)</t>
+        </is>
+      </c>
+      <c r="B98" s="7" t="inlineStr">
+        <is>
+          <t>학교폭력 &gt; 학교폭력의 이해 &gt; 학교폭력의 개념 (학교폭력예방 및 대책에 관한 법률 제2조)</t>
+        </is>
+      </c>
+      <c r="C98" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D98" s="7" t="inlineStr">
+        <is>
           <t>학교폭력</t>
         </is>
       </c>
-      <c r="E97" s="15" t="inlineStr">
+      <c r="E98" s="12" t="inlineStr">
         <is>
           <t>https://www.easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=1408&amp;ccfNo=1&amp;cciNo=1&amp;cnpClsNo=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="14" t="inlineStr">
+        <is>
+          <t>행정안전부</t>
+        </is>
+      </c>
+      <c r="B99" s="14" t="inlineStr">
+        <is>
+          <t>어린이 안전 배움터 - 자전거 안전(놀이기구)</t>
+        </is>
+      </c>
+      <c r="C99" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D99" s="14" t="inlineStr">
+        <is>
+          <t>안전</t>
+        </is>
+      </c>
+      <c r="E99" s="15" t="inlineStr">
+        <is>
+          <t>https://www.mois.go.kr/chd/sub/a06/play/screen.do</t>
         </is>
       </c>
     </row>
@@ -30379,6 +30429,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E95" r:id="rId70"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E96" r:id="rId71"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E97" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E98" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E99" r:id="rId74"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/quiz/수업도우미_퀴즈_문항과출처.xlsx
+++ b/quiz/수업도우미_퀴즈_문항과출처.xlsx
@@ -11865,7 +11865,7 @@
       </c>
       <c r="D122" s="14" t="inlineStr">
         <is>
-          <t>틀려요! 내려오는 친구와 부딪혀 크게 다칠 수 있어요.</t>
+          <t>틀려요! 미끄럼판으로 올라가지 않고 반드시 계단을 이용해요.</t>
         </is>
       </c>
       <c r="E122" s="14" t="inlineStr">
@@ -11875,17 +11875,17 @@
       </c>
       <c r="F122" s="14" t="inlineStr">
         <is>
-          <t>행정안전부</t>
+          <t>법제처(찾기쉬운 생활법령정보)</t>
         </is>
       </c>
       <c r="G122" s="14" t="inlineStr">
         <is>
-          <t>어린이 안전 배움터 - 놀이기구(놀이터 안전)</t>
+          <t>찾기쉬운 생활법령정보 - 어린이놀이시설에서의 안전수칙</t>
         </is>
       </c>
       <c r="H122" s="15" t="inlineStr">
         <is>
-          <t>https://www.mois.go.kr/chd/sub/a06/play_2/screen.do</t>
+          <t>https://easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=690&amp;ccfNo=4&amp;cciNo=2&amp;cnpClsNo=1</t>
         </is>
       </c>
     </row>
@@ -11905,7 +11905,7 @@
       </c>
       <c r="D123" s="7" t="inlineStr">
         <is>
-          <t>맞아요! 뛰어내리면 크게 다칠 수 있어요.</t>
+          <t>맞아요! 줄을 양손으로 잡고 타며 움직이는 도중에 뛰어내리지 않아요.</t>
         </is>
       </c>
       <c r="E123" s="7" t="inlineStr">
@@ -11915,17 +11915,17 @@
       </c>
       <c r="F123" s="7" t="inlineStr">
         <is>
-          <t>행정안전부</t>
+          <t>법제처(찾기쉬운 생활법령정보)</t>
         </is>
       </c>
       <c r="G123" s="7" t="inlineStr">
         <is>
-          <t>어린이 안전 배움터 - 놀이기구(놀이터 안전)</t>
+          <t>찾기쉬운 생활법령정보 - 어린이놀이시설에서의 안전수칙</t>
         </is>
       </c>
       <c r="H123" s="12" t="inlineStr">
         <is>
-          <t>https://www.mois.go.kr/chd/sub/a06/play_2/screen.do</t>
+          <t>https://easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=690&amp;ccfNo=4&amp;cciNo=2&amp;cnpClsNo=1</t>
         </is>
       </c>
     </row>
@@ -11945,7 +11945,7 @@
       </c>
       <c r="D124" s="14" t="inlineStr">
         <is>
-          <t>아니요! 그네에 부딪힐 수 있으니 돌아서 지나가요.</t>
+          <t>아니요! 다른 사람이 타고 있을 때는 앞뒤로 지나가지 않아요.</t>
         </is>
       </c>
       <c r="E124" s="14" t="inlineStr">
@@ -11955,17 +11955,17 @@
       </c>
       <c r="F124" s="14" t="inlineStr">
         <is>
-          <t>행정안전부</t>
+          <t>법제처(찾기쉬운 생활법령정보)</t>
         </is>
       </c>
       <c r="G124" s="14" t="inlineStr">
         <is>
-          <t>어린이 안전 배움터 - 놀이기구(놀이터 안전)</t>
+          <t>찾기쉬운 생활법령정보 - 어린이놀이시설에서의 안전수칙</t>
         </is>
       </c>
       <c r="H124" s="15" t="inlineStr">
         <is>
-          <t>https://www.mois.go.kr/chd/sub/a06/play_2/screen.do</t>
+          <t>https://easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=690&amp;ccfNo=4&amp;cciNo=2&amp;cnpClsNo=1</t>
         </is>
       </c>
     </row>
@@ -11975,7 +11975,7 @@
       </c>
       <c r="B125" s="7" t="inlineStr">
         <is>
-          <t>놀이터에서 놀 때 목도리나 끈이 긴 옷은 기구에 걸릴 수 있어 위험해요.</t>
+          <t>그네를 탈 때는 줄을 양손으로 꼭 잡아요.</t>
         </is>
       </c>
       <c r="C125" s="6" t="inlineStr">
@@ -11985,7 +11985,7 @@
       </c>
       <c r="D125" s="7" t="inlineStr">
         <is>
-          <t>맞아요! 끈이 걸리면 목이 조일 수 있어 매우 위험해요.</t>
+          <t>맞아요! 줄을 양손으로 잡고 타야 안전해요.</t>
         </is>
       </c>
       <c r="E125" s="7" t="inlineStr">
@@ -11995,17 +11995,17 @@
       </c>
       <c r="F125" s="7" t="inlineStr">
         <is>
-          <t>행정안전부</t>
+          <t>법제처(찾기쉬운 생활법령정보)</t>
         </is>
       </c>
       <c r="G125" s="7" t="inlineStr">
         <is>
-          <t>어린이 안전 배움터 - 놀이기구(놀이터 안전)</t>
+          <t>찾기쉬운 생활법령정보 - 어린이놀이시설에서의 안전수칙</t>
         </is>
       </c>
       <c r="H125" s="12" t="inlineStr">
         <is>
-          <t>https://www.mois.go.kr/chd/sub/a06/play_2/screen.do</t>
+          <t>https://easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=690&amp;ccfNo=4&amp;cciNo=2&amp;cnpClsNo=1</t>
         </is>
       </c>
     </row>
@@ -28184,7 +28184,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E99"/>
+  <dimension ref="A1:E100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -28239,7 +28239,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="C6" s="16">
         <f>B6/$B$22</f>
@@ -28249,11 +28249,11 @@
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>행정안전부</t>
+          <t>기후에너지환경부</t>
         </is>
       </c>
       <c r="B7" s="13" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C7" s="17">
         <f>B7/$B$22</f>
@@ -28263,11 +28263,11 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>기후에너지환경부</t>
+          <t>행정안전부</t>
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C8" s="16">
         <f>B8/$B$22</f>
@@ -28474,7 +28474,7 @@
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t>문서별 (74종)</t>
+          <t>문서별 (75종)</t>
         </is>
       </c>
     </row>
@@ -28913,7 +28913,7 @@
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>어린이 안전 배움터 - 놀이기구(놀이터 안전)</t>
+          <t>국민안전24(옛 국민재난안전포털) - 태풍 국민행동요령</t>
         </is>
       </c>
       <c r="C42" s="6" t="n">
@@ -28926,7 +28926,7 @@
       </c>
       <c r="E42" s="12" t="inlineStr">
         <is>
-          <t>https://www.mois.go.kr/chd/sub/a06/play_2/screen.do</t>
+          <t>https://www.safekorea.go.kr/safekorea-kor/acts/nacts/action-guide.do?category=typhoon&amp;actsHeaderTitle=%ED%83%9C%ED%92%8D&amp;menuSn=4</t>
         </is>
       </c>
     </row>
@@ -28938,7 +28938,7 @@
       </c>
       <c r="B43" s="14" t="inlineStr">
         <is>
-          <t>국민안전24(옛 국민재난안전포털) - 태풍 국민행동요령</t>
+          <t>어린이 안전 배움터 - 여름철 안전(물놀이)</t>
         </is>
       </c>
       <c r="C43" s="13" t="n">
@@ -28951,44 +28951,44 @@
       </c>
       <c r="E43" s="15" t="inlineStr">
         <is>
-          <t>https://www.safekorea.go.kr/safekorea-kor/acts/nacts/action-guide.do?category=typhoon&amp;actsHeaderTitle=%ED%83%9C%ED%92%8D&amp;menuSn=4</t>
+          <t>https://www.mois.go.kr/chd/sub/a06/summer/screen.do</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>행정안전부</t>
+          <t>법제처(찾기쉬운 생활법령정보)</t>
         </is>
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>어린이 안전 배움터 - 여름철 안전(물놀이)</t>
+          <t>학교폭력 &gt; 학교폭력 신고 및 초기대응 &gt; 학교폭력의 신고 및 고발</t>
         </is>
       </c>
       <c r="C44" s="6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>안전</t>
+          <t>학교폭력</t>
         </is>
       </c>
       <c r="E44" s="12" t="inlineStr">
         <is>
-          <t>https://www.mois.go.kr/chd/sub/a06/summer/screen.do</t>
+          <t>https://easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=1408&amp;ccfNo=3&amp;cciNo=1&amp;cnpClsNo=1</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="14" t="inlineStr">
         <is>
-          <t>법제처(찾기쉬운 생활법령정보)</t>
+          <t>한국환경보전원 탄소중립 정책포털</t>
         </is>
       </c>
       <c r="B45" s="14" t="inlineStr">
         <is>
-          <t>학교폭력 &gt; 학교폭력 신고 및 초기대응 &gt; 학교폭력의 신고 및 고발</t>
+          <t>기후변화 - 온실가스와 온실효과</t>
         </is>
       </c>
       <c r="C45" s="13" t="n">
@@ -28996,24 +28996,24 @@
       </c>
       <c r="D45" s="14" t="inlineStr">
         <is>
-          <t>학교폭력</t>
+          <t>환경</t>
         </is>
       </c>
       <c r="E45" s="15" t="inlineStr">
         <is>
-          <t>https://easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=1408&amp;ccfNo=3&amp;cciNo=1&amp;cnpClsNo=1</t>
+          <t>https://www.gihoo.or.kr/menu.es?mid=a30101010000</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>한국환경보전원 탄소중립 정책포털</t>
+          <t>행정안전부</t>
         </is>
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>기후변화 - 온실가스와 온실효과</t>
+          <t>어린이 안전 배움터 - 도로·교통(어린이보호구역 교통안전수칙)</t>
         </is>
       </c>
       <c r="C46" s="6" t="n">
@@ -29021,49 +29021,49 @@
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>환경</t>
+          <t>안전</t>
         </is>
       </c>
       <c r="E46" s="12" t="inlineStr">
         <is>
-          <t>https://www.gihoo.or.kr/menu.es?mid=a30101010000</t>
+          <t>https://www.mois.go.kr/chd/sub/a06/road/screen.do</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="14" t="inlineStr">
         <is>
-          <t>행정안전부</t>
+          <t>대한민국 정책브리핑(문화체육관광부 운영)</t>
         </is>
       </c>
       <c r="B47" s="14" t="inlineStr">
         <is>
-          <t>어린이 안전 배움터 - 도로·교통(어린이보호구역 교통안전수칙)</t>
+          <t>여름철 전기절약 행동요령</t>
         </is>
       </c>
       <c r="C47" s="13" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D47" s="14" t="inlineStr">
         <is>
-          <t>안전</t>
+          <t>환경</t>
         </is>
       </c>
       <c r="E47" s="15" t="inlineStr">
         <is>
-          <t>https://www.mois.go.kr/chd/sub/a06/road/screen.do</t>
+          <t>https://www.korea.kr/news/policyNewsView.do?newsId=148736371</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>대한민국 정책브리핑(문화체육관광부 운영)</t>
+          <t>법제처(찾기쉬운 생활법령정보)</t>
         </is>
       </c>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>여름철 전기절약 행동요령</t>
+          <t>학교폭력 &gt; 학교폭력의 이해 &gt; 학교폭력의 개념 (학교폭력예방 및 대책에 관한 법률 제2조제1호의2)</t>
         </is>
       </c>
       <c r="C48" s="6" t="n">
@@ -29071,12 +29071,12 @@
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>환경</t>
+          <t>학교폭력</t>
         </is>
       </c>
       <c r="E48" s="12" t="inlineStr">
         <is>
-          <t>https://www.korea.kr/news/policyNewsView.do?newsId=148736371</t>
+          <t>https://www.easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=1408&amp;ccfNo=1&amp;cciNo=1&amp;cnpClsNo=1</t>
         </is>
       </c>
     </row>
@@ -29088,7 +29088,7 @@
       </c>
       <c r="B49" s="14" t="inlineStr">
         <is>
-          <t>학교폭력 &gt; 학교폭력의 이해 &gt; 학교폭력의 개념 (학교폭력예방 및 대책에 관한 법률 제2조제1호의2)</t>
+          <t>학교폭력 &gt; 학교폭력의 해결 &gt; 피해학생에 대한 보호 조치 (학교폭력예방 및 대책에 관한 법률 제16조)</t>
         </is>
       </c>
       <c r="C49" s="13" t="n">
@@ -29101,19 +29101,19 @@
       </c>
       <c r="E49" s="15" t="inlineStr">
         <is>
-          <t>https://www.easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=1408&amp;ccfNo=1&amp;cciNo=1&amp;cnpClsNo=1</t>
+          <t>https://easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=1408&amp;ccfNo=4&amp;cciNo=2&amp;cnpClsNo=3</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t>법제처(찾기쉬운 생활법령정보)</t>
+          <t>한국에너지공단</t>
         </is>
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>학교폭력 &gt; 학교폭력의 해결 &gt; 피해학생에 대한 보호 조치 (학교폭력예방 및 대책에 관한 법률 제16조)</t>
+          <t>보도자료 - 일상 속 작은 실천이 난방비 절약의 핵심(2025.2.28.)</t>
         </is>
       </c>
       <c r="C50" s="6" t="n">
@@ -29121,49 +29121,49 @@
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>학교폭력</t>
+          <t>환경</t>
         </is>
       </c>
       <c r="E50" s="12" t="inlineStr">
         <is>
-          <t>https://easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=1408&amp;ccfNo=4&amp;cciNo=2&amp;cnpClsNo=3</t>
+          <t>https://www.energy.or.kr/front/board/View3.do?boardMngNo=3&amp;boardNo=10024875</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="14" t="inlineStr">
         <is>
-          <t>한국에너지공단</t>
+          <t>교육부(위(Wee) 프로젝트)</t>
         </is>
       </c>
       <c r="B51" s="14" t="inlineStr">
         <is>
-          <t>보도자료 - 일상 속 작은 실천이 난방비 절약의 핵심(2025.2.28.)</t>
+          <t>위(Wee) 프로젝트 소개</t>
         </is>
       </c>
       <c r="C51" s="13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D51" s="14" t="inlineStr">
         <is>
-          <t>환경</t>
+          <t>학교폭력</t>
         </is>
       </c>
       <c r="E51" s="15" t="inlineStr">
         <is>
-          <t>https://www.energy.or.kr/front/board/View3.do?boardMngNo=3&amp;boardNo=10024875</t>
+          <t>https://www.wee.go.kr/menu?menuKey=eE85uGkNYN</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t>교육부(위(Wee) 프로젝트)</t>
+          <t>기상청</t>
         </is>
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>위(Wee) 프로젝트 소개</t>
+          <t>어린이 기상교실 - 지구온난화</t>
         </is>
       </c>
       <c r="C52" s="6" t="n">
@@ -29171,24 +29171,24 @@
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>학교폭력</t>
+          <t>환경</t>
         </is>
       </c>
       <c r="E52" s="12" t="inlineStr">
         <is>
-          <t>https://www.wee.go.kr/menu?menuKey=eE85uGkNYN</t>
+          <t>https://www.kma.go.kr/kids/231.jsp</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="14" t="inlineStr">
         <is>
-          <t>기상청</t>
+          <t>대한민국 정책브리핑(문화체육관광부 운영)</t>
         </is>
       </c>
       <c r="B53" s="14" t="inlineStr">
         <is>
-          <t>어린이 기상교실 - 지구온난화</t>
+          <t>[Q&amp;A] 투명 페트병, 어떻게 분리배출해야 하나</t>
         </is>
       </c>
       <c r="C53" s="13" t="n">
@@ -29201,19 +29201,19 @@
       </c>
       <c r="E53" s="15" t="inlineStr">
         <is>
-          <t>https://www.kma.go.kr/kids/231.jsp</t>
+          <t>https://www.korea.kr/news/policyNewsView.do?newsId=148881706</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t>대한민국 정책브리핑(문화체육관광부 운영)</t>
+          <t>법제처(찾기쉬운 생활법령정보)</t>
         </is>
       </c>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>[Q&amp;A] 투명 페트병, 어떻게 분리배출해야 하나</t>
+          <t>찾기쉬운 생활법령정보 - 화재예방을 위한 안전수칙</t>
         </is>
       </c>
       <c r="C54" s="6" t="n">
@@ -29221,12 +29221,12 @@
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>환경</t>
+          <t>안전</t>
         </is>
       </c>
       <c r="E54" s="12" t="inlineStr">
         <is>
-          <t>https://www.korea.kr/news/policyNewsView.do?newsId=148881706</t>
+          <t>https://easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=690&amp;ccfNo=5&amp;cciNo=1&amp;cnpClsNo=1</t>
         </is>
       </c>
     </row>
@@ -29238,7 +29238,7 @@
       </c>
       <c r="B55" s="14" t="inlineStr">
         <is>
-          <t>찾기쉬운 생활법령정보 - 화재예방을 위한 안전수칙</t>
+          <t>찾기쉬운 생활법령정보 - 화재예방을 위한 안전수칙(화상 응급처치)</t>
         </is>
       </c>
       <c r="C55" s="13" t="n">
@@ -29258,12 +29258,12 @@
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t>법제처(찾기쉬운 생활법령정보)</t>
+          <t>행정안전부</t>
         </is>
       </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>찾기쉬운 생활법령정보 - 화재예방을 위한 안전수칙(화상 응급처치)</t>
+          <t>국민안전24(옛 국민재난안전포털) - 폭염 국민행동요령</t>
         </is>
       </c>
       <c r="C56" s="6" t="n">
@@ -29276,7 +29276,7 @@
       </c>
       <c r="E56" s="12" t="inlineStr">
         <is>
-          <t>https://easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=690&amp;ccfNo=5&amp;cciNo=1&amp;cnpClsNo=1</t>
+          <t>https://www.safekorea.go.kr/safekorea-kor/acts/nacts/action-guide.do?category=heatWave&amp;actsHeaderTitle=%ED%8F%AD%EC%97%BC&amp;menuSn=4</t>
         </is>
       </c>
     </row>
@@ -29288,7 +29288,7 @@
       </c>
       <c r="B57" s="14" t="inlineStr">
         <is>
-          <t>국민안전24(옛 국민재난안전포털) - 폭염 국민행동요령</t>
+          <t>국민안전24(옛 국민재난안전포털) - 한파 국민행동요령</t>
         </is>
       </c>
       <c r="C57" s="13" t="n">
@@ -29301,44 +29301,44 @@
       </c>
       <c r="E57" s="15" t="inlineStr">
         <is>
-          <t>https://www.safekorea.go.kr/safekorea-kor/acts/nacts/action-guide.do?category=heatWave&amp;actsHeaderTitle=%ED%8F%AD%EC%97%BC&amp;menuSn=4</t>
+          <t>https://www.safekorea.go.kr/safekorea-kor/acts/nacts/action-guide.do?category=coldWave&amp;actsHeaderTitle=%ED%95%9C%ED%8C%8C&amp;menuSn=4</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="inlineStr">
         <is>
-          <t>행정안전부</t>
+          <t>기후에너지환경부</t>
         </is>
       </c>
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t>국민안전24(옛 국민재난안전포털) - 한파 국민행동요령</t>
+          <t>카드뉴스 - '약 버리는 법' 약국, 보건소 분리수거함을 이용하세요!</t>
         </is>
       </c>
       <c r="C58" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>안전</t>
+          <t>환경</t>
         </is>
       </c>
       <c r="E58" s="12" t="inlineStr">
         <is>
-          <t>https://www.safekorea.go.kr/safekorea-kor/acts/nacts/action-guide.do?category=coldWave&amp;actsHeaderTitle=%ED%95%9C%ED%8C%8C&amp;menuSn=4</t>
+          <t>https://mcee.go.kr/home/web/board/read.do?boardId=862840&amp;boardMasterId=713&amp;menuId=10392</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="14" t="inlineStr">
         <is>
-          <t>기후에너지환경부</t>
+          <t>방송미디어통신위원회(옛 방송통신위원회)·한국지능정보사회진흥원</t>
         </is>
       </c>
       <c r="B59" s="14" t="inlineStr">
         <is>
-          <t>카드뉴스 - '약 버리는 법' 약국, 보건소 분리수거함을 이용하세요!</t>
+          <t>2023년도 사이버폭력 실태조사 결과 발표(보도자료)</t>
         </is>
       </c>
       <c r="C59" s="13" t="n">
@@ -29346,24 +29346,24 @@
       </c>
       <c r="D59" s="14" t="inlineStr">
         <is>
-          <t>환경</t>
+          <t>학교폭력</t>
         </is>
       </c>
       <c r="E59" s="15" t="inlineStr">
         <is>
-          <t>https://mcee.go.kr/home/web/board/read.do?boardId=862840&amp;boardMasterId=713&amp;menuId=10392</t>
+          <t>https://www.kmcc.go.kr/user.do?boardId=1113&amp;page=A05030000&amp;dc=K00000200&amp;boardSeq=60294&amp;mode=view</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="inlineStr">
         <is>
-          <t>방송미디어통신위원회(옛 방송통신위원회)·한국지능정보사회진흥원</t>
+          <t>법제처(찾기쉬운 생활법령정보)</t>
         </is>
       </c>
       <c r="B60" s="7" t="inlineStr">
         <is>
-          <t>2023년도 사이버폭력 실태조사 결과 발표(보도자료)</t>
+          <t>찾기쉬운 생활법령정보 - 어린이 물놀이 안전</t>
         </is>
       </c>
       <c r="C60" s="6" t="n">
@@ -29371,12 +29371,12 @@
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>학교폭력</t>
+          <t>안전</t>
         </is>
       </c>
       <c r="E60" s="12" t="inlineStr">
         <is>
-          <t>https://www.kmcc.go.kr/user.do?boardId=1113&amp;page=A05030000&amp;dc=K00000200&amp;boardSeq=60294&amp;mode=view</t>
+          <t>https://easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=690&amp;ccfNo=4&amp;cciNo=1&amp;cnpClsNo=1</t>
         </is>
       </c>
     </row>
@@ -29388,7 +29388,7 @@
       </c>
       <c r="B61" s="14" t="inlineStr">
         <is>
-          <t>찾기쉬운 생활법령정보 - 어린이 물놀이 안전</t>
+          <t>찾기쉬운 생활법령정보 - 어린이놀이시설에서의 안전수칙</t>
         </is>
       </c>
       <c r="C61" s="13" t="n">
@@ -29401,7 +29401,7 @@
       </c>
       <c r="E61" s="15" t="inlineStr">
         <is>
-          <t>https://easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=690&amp;ccfNo=4&amp;cciNo=1&amp;cnpClsNo=1</t>
+          <t>https://easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=690&amp;ccfNo=4&amp;cciNo=2&amp;cnpClsNo=1</t>
         </is>
       </c>
     </row>
@@ -29558,25 +29558,25 @@
     <row r="68">
       <c r="A68" s="7" t="inlineStr">
         <is>
-          <t>교육부</t>
+          <t>행정안전부</t>
         </is>
       </c>
       <c r="B68" s="7" t="inlineStr">
         <is>
-          <t>학교 디지털 성폭력 초기 대응을 위한 '디지털 성폭력 에스오에스(SOS) 가이드' 발간(보도자료, 2025.4.22.)</t>
+          <t>어린이 안전 배움터 - 놀이기구(놀이터 안전)</t>
         </is>
       </c>
       <c r="C68" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>학교폭력</t>
+          <t>안전</t>
         </is>
       </c>
       <c r="E68" s="12" t="inlineStr">
         <is>
-          <t>https://www.moe.go.kr/boardCnts/viewRenew.do?boardID=294&amp;boardSeq=103170&amp;lev=0&amp;statusYN=W&amp;s=moe&amp;m=020402&amp;opType=N</t>
+          <t>https://www.mois.go.kr/chd/sub/a06/play_2/screen.do</t>
         </is>
       </c>
     </row>
@@ -29588,7 +29588,7 @@
       </c>
       <c r="B69" s="14" t="inlineStr">
         <is>
-          <t>학교폭력 예방교육! 공감과 소통의 '어울림 프로그램'과 함께해요 (보도자료, 2019.1.30.)</t>
+          <t>학교 디지털 성폭력 초기 대응을 위한 '디지털 성폭력 에스오에스(SOS) 가이드' 발간(보도자료, 2025.4.22.)</t>
         </is>
       </c>
       <c r="C69" s="13" t="n">
@@ -29601,19 +29601,19 @@
       </c>
       <c r="E69" s="15" t="inlineStr">
         <is>
-          <t>https://www.moe.go.kr/boardCnts/view.do?boardID=294&amp;boardSeq=76637&amp;lev=0&amp;statusYN=W&amp;s=moe&amp;m=020402&amp;opType=N</t>
+          <t>https://www.moe.go.kr/boardCnts/viewRenew.do?boardID=294&amp;boardSeq=103170&amp;lev=0&amp;statusYN=W&amp;s=moe&amp;m=020402&amp;opType=N</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="inlineStr">
         <is>
-          <t>기상청</t>
+          <t>교육부</t>
         </is>
       </c>
       <c r="B70" s="7" t="inlineStr">
         <is>
-          <t>보도자료 - 2025년 우리나라 이산화탄소 농도, 또 최고치 경신</t>
+          <t>학교폭력 예방교육! 공감과 소통의 '어울림 프로그램'과 함께해요 (보도자료, 2019.1.30.)</t>
         </is>
       </c>
       <c r="C70" s="6" t="n">
@@ -29621,24 +29621,24 @@
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>환경</t>
+          <t>학교폭력</t>
         </is>
       </c>
       <c r="E70" s="12" t="inlineStr">
         <is>
-          <t>https://www.kma.go.kr/kma/news/press_01.jsp?mode=view&amp;num=1194641</t>
+          <t>https://www.moe.go.kr/boardCnts/view.do?boardID=294&amp;boardSeq=76637&amp;lev=0&amp;statusYN=W&amp;s=moe&amp;m=020402&amp;opType=N</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="14" t="inlineStr">
         <is>
-          <t>대한민국 정책브리핑(문화체육관광부 운영)</t>
+          <t>기상청</t>
         </is>
       </c>
       <c r="B71" s="14" t="inlineStr">
         <is>
-          <t>새 학기, 자녀와 함께 교통안전수칙 알아봤습니다! (횡단보도 5원칙)</t>
+          <t>보도자료 - 2025년 우리나라 이산화탄소 농도, 또 최고치 경신</t>
         </is>
       </c>
       <c r="C71" s="13" t="n">
@@ -29646,24 +29646,24 @@
       </c>
       <c r="D71" s="14" t="inlineStr">
         <is>
-          <t>안전</t>
+          <t>환경</t>
         </is>
       </c>
       <c r="E71" s="15" t="inlineStr">
         <is>
-          <t>https://www.korea.kr/news/policyNewsView.do?newsId=148926855</t>
+          <t>https://www.kma.go.kr/kma/news/press_01.jsp?mode=view&amp;num=1194641</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="7" t="inlineStr">
         <is>
-          <t>법제처(찾기쉬운 생활법령정보)</t>
+          <t>대한민국 정책브리핑(문화체육관광부 운영)</t>
         </is>
       </c>
       <c r="B72" s="7" t="inlineStr">
         <is>
-          <t>찾기쉬운 생활법령정보 - 어린이통학버스의 안전설비</t>
+          <t>새 학기, 자녀와 함께 교통안전수칙 알아봤습니다! (횡단보도 5원칙)</t>
         </is>
       </c>
       <c r="C72" s="6" t="n">
@@ -29676,7 +29676,7 @@
       </c>
       <c r="E72" s="12" t="inlineStr">
         <is>
-          <t>https://easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=690&amp;ccfNo=1&amp;cciNo=2&amp;cnpClsNo=2</t>
+          <t>https://www.korea.kr/news/policyNewsView.do?newsId=148926855</t>
         </is>
       </c>
     </row>
@@ -29688,7 +29688,7 @@
       </c>
       <c r="B73" s="14" t="inlineStr">
         <is>
-          <t>학교폭력 &gt; 학교폭력의 해결 &gt; 가해학생에 대한 조치 (학교폭력예방 및 대책에 관한 법률 제17조)</t>
+          <t>찾기쉬운 생활법령정보 - 어린이통학버스의 안전설비</t>
         </is>
       </c>
       <c r="C73" s="13" t="n">
@@ -29696,12 +29696,12 @@
       </c>
       <c r="D73" s="14" t="inlineStr">
         <is>
-          <t>학교폭력</t>
+          <t>안전</t>
         </is>
       </c>
       <c r="E73" s="15" t="inlineStr">
         <is>
-          <t>https://easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=1408&amp;ccfNo=4&amp;cciNo=2&amp;cnpClsNo=6</t>
+          <t>https://easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=690&amp;ccfNo=1&amp;cciNo=2&amp;cnpClsNo=2</t>
         </is>
       </c>
     </row>
@@ -29713,7 +29713,7 @@
       </c>
       <c r="B74" s="7" t="inlineStr">
         <is>
-          <t>청소년의 인터넷 이용하기 &gt; 댓글을 다는 경우 &gt; 인터넷 명예훼손에 대처하는 방법 (정보통신망법 제70조제1항)</t>
+          <t>학교폭력 &gt; 학교폭력의 해결 &gt; 가해학생에 대한 조치 (학교폭력예방 및 대책에 관한 법률 제17조)</t>
         </is>
       </c>
       <c r="C74" s="6" t="n">
@@ -29726,7 +29726,7 @@
       </c>
       <c r="E74" s="12" t="inlineStr">
         <is>
-          <t>https://easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=659&amp;ccfNo=6&amp;cciNo=2&amp;cnpClsNo=1</t>
+          <t>https://easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=1408&amp;ccfNo=4&amp;cciNo=2&amp;cnpClsNo=6</t>
         </is>
       </c>
     </row>
@@ -29738,7 +29738,7 @@
       </c>
       <c r="B75" s="14" t="inlineStr">
         <is>
-          <t>학교폭력 &gt; 학교폭력 신고 및 초기대응 &gt; 학교폭력의 신고 및 고발 (학교폭력예방 및 대책에 관한 법률 제20조제5항)</t>
+          <t>청소년의 인터넷 이용하기 &gt; 댓글을 다는 경우 &gt; 인터넷 명예훼손에 대처하는 방법 (정보통신망법 제70조제1항)</t>
         </is>
       </c>
       <c r="C75" s="13" t="n">
@@ -29751,19 +29751,19 @@
       </c>
       <c r="E75" s="15" t="inlineStr">
         <is>
-          <t>https://easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=1408&amp;ccfNo=3&amp;cciNo=1&amp;cnpClsNo=1</t>
+          <t>https://easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=659&amp;ccfNo=6&amp;cciNo=2&amp;cnpClsNo=1</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="7" t="inlineStr">
         <is>
-          <t>행정안전부</t>
+          <t>법제처(찾기쉬운 생활법령정보)</t>
         </is>
       </c>
       <c r="B76" s="7" t="inlineStr">
         <is>
-          <t>어린이 안전 배움터 - 구조·구급(119 구급신고요령)</t>
+          <t>학교폭력 &gt; 학교폭력 신고 및 초기대응 &gt; 학교폭력의 신고 및 고발 (학교폭력예방 및 대책에 관한 법률 제20조제5항)</t>
         </is>
       </c>
       <c r="C76" s="6" t="n">
@@ -29771,49 +29771,49 @@
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>안전</t>
+          <t>학교폭력</t>
         </is>
       </c>
       <c r="E76" s="12" t="inlineStr">
         <is>
-          <t>https://www.mois.go.kr/chd/sub/a06/rescue/screen.do</t>
+          <t>https://easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=1408&amp;ccfNo=3&amp;cciNo=1&amp;cnpClsNo=1</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="14" t="inlineStr">
         <is>
-          <t>기상청</t>
+          <t>행정안전부</t>
         </is>
       </c>
       <c r="B77" s="14" t="inlineStr">
         <is>
-          <t>보도자료 - 2025년, 다양한 이상기후로 확인된 '기후위기의 시대'</t>
+          <t>어린이 안전 배움터 - 구조·구급(119 구급신고요령)</t>
         </is>
       </c>
       <c r="C77" s="13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D77" s="14" t="inlineStr">
         <is>
-          <t>환경</t>
+          <t>안전</t>
         </is>
       </c>
       <c r="E77" s="15" t="inlineStr">
         <is>
-          <t>https://www.kma.go.kr/kma/news/press.jsp?bid=press&amp;mode=view&amp;num=1194622</t>
+          <t>https://www.mois.go.kr/chd/sub/a06/rescue/screen.do</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="inlineStr">
         <is>
-          <t>법제처(찾기쉬운 생활법령정보)</t>
+          <t>기상청</t>
         </is>
       </c>
       <c r="B78" s="7" t="inlineStr">
         <is>
-          <t>찾기쉬운 생활법령정보 - 어린이 보행사고 예방을 위한 안전수칙(도로교통법 제10조제2항)</t>
+          <t>보도자료 - 2025년, 다양한 이상기후로 확인된 '기후위기의 시대'</t>
         </is>
       </c>
       <c r="C78" s="6" t="n">
@@ -29821,12 +29821,12 @@
       </c>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>안전</t>
+          <t>환경</t>
         </is>
       </c>
       <c r="E78" s="12" t="inlineStr">
         <is>
-          <t>https://www.easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=690&amp;ccfNo=1&amp;cciNo=1&amp;cnpClsNo=1</t>
+          <t>https://www.kma.go.kr/kma/news/press.jsp?bid=press&amp;mode=view&amp;num=1194622</t>
         </is>
       </c>
     </row>
@@ -29838,7 +29838,7 @@
       </c>
       <c r="B79" s="14" t="inlineStr">
         <is>
-          <t>찾기쉬운 생활법령정보 - 어린이 생활안전(어린이 보호구역)</t>
+          <t>찾기쉬운 생활법령정보 - 어린이 보행사고 예방을 위한 안전수칙(도로교통법 제10조제2항)</t>
         </is>
       </c>
       <c r="C79" s="13" t="n">
@@ -29851,7 +29851,7 @@
       </c>
       <c r="E79" s="15" t="inlineStr">
         <is>
-          <t>https://www.easylaw.go.kr/CSP/CnpClsMainBtr.laf?popMenu=ov&amp;csmSeq=690&amp;ccfNo=1&amp;cciNo=1&amp;cnpClsNo=3</t>
+          <t>https://www.easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=690&amp;ccfNo=1&amp;cciNo=1&amp;cnpClsNo=1</t>
         </is>
       </c>
     </row>
@@ -29863,7 +29863,7 @@
       </c>
       <c r="B80" s="7" t="inlineStr">
         <is>
-          <t>찾기쉬운 생활법령정보 - 가정의 차량 탑승 시 안전수칙(도로교통법 제50조제1항)</t>
+          <t>찾기쉬운 생활법령정보 - 어린이 생활안전(어린이 보호구역)</t>
         </is>
       </c>
       <c r="C80" s="6" t="n">
@@ -29876,7 +29876,7 @@
       </c>
       <c r="E80" s="12" t="inlineStr">
         <is>
-          <t>https://easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=690&amp;ccfNo=1&amp;cciNo=2&amp;cnpClsNo=1</t>
+          <t>https://www.easylaw.go.kr/CSP/CnpClsMainBtr.laf?popMenu=ov&amp;csmSeq=690&amp;ccfNo=1&amp;cciNo=1&amp;cnpClsNo=3</t>
         </is>
       </c>
     </row>
@@ -29888,7 +29888,7 @@
       </c>
       <c r="B81" s="14" t="inlineStr">
         <is>
-          <t>찾기쉬운 생활법령정보 - 가정의 차량 탑승 시 안전수칙(도로교통법 제49조제1항제7호)</t>
+          <t>찾기쉬운 생활법령정보 - 가정의 차량 탑승 시 안전수칙(도로교통법 제50조제1항)</t>
         </is>
       </c>
       <c r="C81" s="13" t="n">
@@ -29913,7 +29913,7 @@
       </c>
       <c r="B82" s="7" t="inlineStr">
         <is>
-          <t>학교폭력 &gt; 사전예방 &gt; 학교폭력 예방교육 실시 (학교폭력예방 및 대책에 관한 법률 제15조)</t>
+          <t>찾기쉬운 생활법령정보 - 가정의 차량 탑승 시 안전수칙(도로교통법 제49조제1항제7호)</t>
         </is>
       </c>
       <c r="C82" s="6" t="n">
@@ -29921,12 +29921,12 @@
       </c>
       <c r="D82" s="7" t="inlineStr">
         <is>
-          <t>학교폭력</t>
+          <t>안전</t>
         </is>
       </c>
       <c r="E82" s="12" t="inlineStr">
         <is>
-          <t>https://www.easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=1408&amp;ccfNo=2&amp;cciNo=2&amp;cnpClsNo=1</t>
+          <t>https://easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=690&amp;ccfNo=1&amp;cciNo=2&amp;cnpClsNo=1</t>
         </is>
       </c>
     </row>
@@ -29938,7 +29938,7 @@
       </c>
       <c r="B83" s="14" t="inlineStr">
         <is>
-          <t>학교폭력 &gt; 학교폭력 신고 및 초기대응 &gt; 학교폭력의 신고 및 고발 (학교폭력예방 및 대책에 관한 법률 제20조)</t>
+          <t>학교폭력 &gt; 사전예방 &gt; 학교폭력 예방교육 실시 (학교폭력예방 및 대책에 관한 법률 제15조)</t>
         </is>
       </c>
       <c r="C83" s="13" t="n">
@@ -29951,7 +29951,7 @@
       </c>
       <c r="E83" s="15" t="inlineStr">
         <is>
-          <t>https://easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=1408&amp;ccfNo=3&amp;cciNo=1&amp;cnpClsNo=1</t>
+          <t>https://www.easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=1408&amp;ccfNo=2&amp;cciNo=2&amp;cnpClsNo=1</t>
         </is>
       </c>
     </row>
@@ -29963,7 +29963,7 @@
       </c>
       <c r="B84" s="7" t="inlineStr">
         <is>
-          <t>학교폭력 &gt; 학교폭력의 해결 &gt; 가해학생에 대한 조치 (학교폭력예방 및 대책에 관한 법률 제17조제1항제2호)</t>
+          <t>학교폭력 &gt; 학교폭력 신고 및 초기대응 &gt; 학교폭력의 신고 및 고발 (학교폭력예방 및 대책에 관한 법률 제20조)</t>
         </is>
       </c>
       <c r="C84" s="6" t="n">
@@ -29976,7 +29976,7 @@
       </c>
       <c r="E84" s="12" t="inlineStr">
         <is>
-          <t>https://easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=1408&amp;ccfNo=4&amp;cciNo=2&amp;cnpClsNo=6</t>
+          <t>https://easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=1408&amp;ccfNo=3&amp;cciNo=1&amp;cnpClsNo=1</t>
         </is>
       </c>
     </row>
@@ -29988,7 +29988,7 @@
       </c>
       <c r="B85" s="14" t="inlineStr">
         <is>
-          <t>학교폭력 &gt; 학교폭력 신고 및 초기대응 &gt; 학교폭력의 신고 및 고발 (학교폭력예방 및 대책에 관한 법률 제20조제4항)</t>
+          <t>학교폭력 &gt; 학교폭력의 해결 &gt; 가해학생에 대한 조치 (학교폭력예방 및 대책에 관한 법률 제17조제1항제2호)</t>
         </is>
       </c>
       <c r="C85" s="13" t="n">
@@ -30001,7 +30001,7 @@
       </c>
       <c r="E85" s="15" t="inlineStr">
         <is>
-          <t>https://easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=1408&amp;ccfNo=3&amp;cciNo=1&amp;cnpClsNo=1</t>
+          <t>https://easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=1408&amp;ccfNo=4&amp;cciNo=2&amp;cnpClsNo=6</t>
         </is>
       </c>
     </row>
@@ -30013,7 +30013,7 @@
       </c>
       <c r="B86" s="7" t="inlineStr">
         <is>
-          <t>학교폭력 &gt; 학교폭력 신고 및 초기대응 &gt; 학교폭력의 신고 및 고발 (학교폭력예방 및 대책에 관한 법률 제21조)</t>
+          <t>학교폭력 &gt; 학교폭력 신고 및 초기대응 &gt; 학교폭력의 신고 및 고발 (학교폭력예방 및 대책에 관한 법률 제20조제4항)</t>
         </is>
       </c>
       <c r="C86" s="6" t="n">
@@ -30026,7 +30026,7 @@
       </c>
       <c r="E86" s="12" t="inlineStr">
         <is>
-          <t>https://www.easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=1408&amp;ccfNo=3&amp;cciNo=1&amp;cnpClsNo=1&amp;menuType=onhunqna</t>
+          <t>https://easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=1408&amp;ccfNo=3&amp;cciNo=1&amp;cnpClsNo=1</t>
         </is>
       </c>
     </row>
@@ -30038,7 +30038,7 @@
       </c>
       <c r="B87" s="14" t="inlineStr">
         <is>
-          <t>학교폭력 &gt; 학교폭력의 해결 &gt; 가해학생에 대한 조치 (학교폭력예방 및 대책에 관한 법률 제17조제1항제1호)</t>
+          <t>학교폭력 &gt; 학교폭력 신고 및 초기대응 &gt; 학교폭력의 신고 및 고발 (학교폭력예방 및 대책에 관한 법률 제21조)</t>
         </is>
       </c>
       <c r="C87" s="13" t="n">
@@ -30051,19 +30051,19 @@
       </c>
       <c r="E87" s="15" t="inlineStr">
         <is>
-          <t>https://easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=1408&amp;ccfNo=4&amp;cciNo=2&amp;cnpClsNo=6</t>
+          <t>https://www.easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=1408&amp;ccfNo=3&amp;cciNo=1&amp;cnpClsNo=1&amp;menuType=onhunqna</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="7" t="inlineStr">
         <is>
-          <t>푸른나무재단</t>
+          <t>법제처(찾기쉬운 생활법령정보)</t>
         </is>
       </c>
       <c r="B88" s="7" t="inlineStr">
         <is>
-          <t>푸른나무재단 청소년 전문 상담·지원 안내</t>
+          <t>학교폭력 &gt; 학교폭력의 해결 &gt; 가해학생에 대한 조치 (학교폭력예방 및 대책에 관한 법률 제17조제1항제1호)</t>
         </is>
       </c>
       <c r="C88" s="6" t="n">
@@ -30076,19 +30076,19 @@
       </c>
       <c r="E88" s="12" t="inlineStr">
         <is>
-          <t>https://btf.or.kr/business/bus01.asp?scrID=0000000108&amp;pageNum=3&amp;subNum=1&amp;ssubNum=1</t>
+          <t>https://easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=1408&amp;ccfNo=4&amp;cciNo=2&amp;cnpClsNo=6</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="14" t="inlineStr">
         <is>
-          <t>한국환경보전원 탄소중립 정책포털</t>
+          <t>푸른나무재단</t>
         </is>
       </c>
       <c r="B89" s="14" t="inlineStr">
         <is>
-          <t>우리나라 기후변화</t>
+          <t>푸른나무재단 청소년 전문 상담·지원 안내</t>
         </is>
       </c>
       <c r="C89" s="13" t="n">
@@ -30096,24 +30096,24 @@
       </c>
       <c r="D89" s="14" t="inlineStr">
         <is>
-          <t>환경</t>
+          <t>학교폭력</t>
         </is>
       </c>
       <c r="E89" s="15" t="inlineStr">
         <is>
-          <t>https://www.gihoo.or.kr/menu.es?mid=a30101030000</t>
+          <t>https://btf.or.kr/business/bus01.asp?scrID=0000000108&amp;pageNum=3&amp;subNum=1&amp;ssubNum=1</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="7" t="inlineStr">
         <is>
-          <t>행정안전부</t>
+          <t>한국환경보전원 탄소중립 정책포털</t>
         </is>
       </c>
       <c r="B90" s="7" t="inlineStr">
         <is>
-          <t>어린이 안전 배움터 - 구조·구급(심폐소생술)</t>
+          <t>우리나라 기후변화</t>
         </is>
       </c>
       <c r="C90" s="6" t="n">
@@ -30121,12 +30121,12 @@
       </c>
       <c r="D90" s="7" t="inlineStr">
         <is>
-          <t>안전</t>
+          <t>환경</t>
         </is>
       </c>
       <c r="E90" s="12" t="inlineStr">
         <is>
-          <t>https://www.mois.go.kr/chd/sub/a06/rescue_3/screen.do</t>
+          <t>https://www.gihoo.or.kr/menu.es?mid=a30101030000</t>
         </is>
       </c>
     </row>
@@ -30138,7 +30138,7 @@
       </c>
       <c r="B91" s="14" t="inlineStr">
         <is>
-          <t>국민안전24 - 전기·가스 사고 국민행동요령</t>
+          <t>어린이 안전 배움터 - 구조·구급(심폐소생술)</t>
         </is>
       </c>
       <c r="C91" s="13" t="n">
@@ -30151,44 +30151,44 @@
       </c>
       <c r="E91" s="15" t="inlineStr">
         <is>
-          <t>https://www.safekorea.go.kr/safekorea-kor/acts/nacts/action-guide.do?category=electircGasAccident&amp;actsHeaderTitle=%EC%A0%84%EA%B8%B0%C2%B7%EA%B0%80%EC%8A%A4+%EC%82%AC%EA%B3%A0&amp;menuSn=4</t>
+          <t>https://www.mois.go.kr/chd/sub/a06/rescue_3/screen.do</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="7" t="inlineStr">
         <is>
-          <t>교육부</t>
+          <t>행정안전부</t>
         </is>
       </c>
       <c r="B92" s="7" t="inlineStr">
         <is>
-          <t>초1·2 학폭 심의 전 '관계회복 프로그램' 우선 실시 (정책브리핑, 2025.4.30.)</t>
+          <t>국민안전24 - 전기·가스 사고 국민행동요령</t>
         </is>
       </c>
       <c r="C92" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D92" s="7" t="inlineStr">
         <is>
-          <t>학교폭력</t>
+          <t>안전</t>
         </is>
       </c>
       <c r="E92" s="12" t="inlineStr">
         <is>
-          <t>https://www.korea.kr/news/policyNewsView.do?newsId=148942634</t>
+          <t>https://www.safekorea.go.kr/safekorea-kor/acts/nacts/action-guide.do?category=electircGasAccident&amp;actsHeaderTitle=%EC%A0%84%EA%B8%B0%C2%B7%EA%B0%80%EC%8A%A4+%EC%82%AC%EA%B3%A0&amp;menuSn=4</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="14" t="inlineStr">
         <is>
-          <t>대한민국 정책브리핑(문화체육관광부 운영)</t>
+          <t>교육부</t>
         </is>
       </c>
       <c r="B93" s="14" t="inlineStr">
         <is>
-          <t>어린이 교통안전 수칙을 지켜라</t>
+          <t>초1·2 학폭 심의 전 '관계회복 프로그램' 우선 실시 (정책브리핑, 2025.4.30.)</t>
         </is>
       </c>
       <c r="C93" s="13" t="n">
@@ -30196,24 +30196,24 @@
       </c>
       <c r="D93" s="14" t="inlineStr">
         <is>
-          <t>안전</t>
+          <t>학교폭력</t>
         </is>
       </c>
       <c r="E93" s="15" t="inlineStr">
         <is>
-          <t>https://www.korea.kr/news/policyNewsView.do?newsId=148954485</t>
+          <t>https://www.korea.kr/news/policyNewsView.do?newsId=148942634</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="7" t="inlineStr">
         <is>
-          <t>법제처(찾기쉬운 생활법령정보)</t>
+          <t>대한민국 정책브리핑(문화체육관광부 운영)</t>
         </is>
       </c>
       <c r="B94" s="7" t="inlineStr">
         <is>
-          <t>찾기쉬운 생활법령정보 - 어린이 자전거 안전(도로교통법 제11조제3항)</t>
+          <t>어린이 교통안전 수칙을 지켜라</t>
         </is>
       </c>
       <c r="C94" s="6" t="n">
@@ -30226,7 +30226,7 @@
       </c>
       <c r="E94" s="12" t="inlineStr">
         <is>
-          <t>https://www.easylaw.go.kr/CSP/CnpClsMainBtr.laf?popMenu=ov&amp;csmSeq=690&amp;ccfNo=1&amp;cciNo=3&amp;cnpClsNo=1</t>
+          <t>https://www.korea.kr/news/policyNewsView.do?newsId=148954485</t>
         </is>
       </c>
     </row>
@@ -30238,7 +30238,7 @@
       </c>
       <c r="B95" s="14" t="inlineStr">
         <is>
-          <t>찾기쉬운 생활법령정보 - 어린이 자전거 안전(도로교통법 제13조의2제6항)</t>
+          <t>찾기쉬운 생활법령정보 - 어린이 자전거 안전(도로교통법 제11조제3항)</t>
         </is>
       </c>
       <c r="C95" s="13" t="n">
@@ -30263,7 +30263,7 @@
       </c>
       <c r="B96" s="7" t="inlineStr">
         <is>
-          <t>찾기쉬운 생활법령정보 - 어린이 자전거 안전(도로교통법 제13조의2제2항)</t>
+          <t>찾기쉬운 생활법령정보 - 어린이 자전거 안전(도로교통법 제13조의2제6항)</t>
         </is>
       </c>
       <c r="C96" s="6" t="n">
@@ -30288,7 +30288,7 @@
       </c>
       <c r="B97" s="14" t="inlineStr">
         <is>
-          <t>찾기쉬운 생활법령정보 - 어린이 자전거 안전</t>
+          <t>찾기쉬운 생활법령정보 - 어린이 자전거 안전(도로교통법 제13조의2제2항)</t>
         </is>
       </c>
       <c r="C97" s="13" t="n">
@@ -30313,7 +30313,7 @@
       </c>
       <c r="B98" s="7" t="inlineStr">
         <is>
-          <t>학교폭력 &gt; 학교폭력의 이해 &gt; 학교폭력의 개념 (학교폭력예방 및 대책에 관한 법률 제2조)</t>
+          <t>찾기쉬운 생활법령정보 - 어린이 자전거 안전</t>
         </is>
       </c>
       <c r="C98" s="6" t="n">
@@ -30321,24 +30321,24 @@
       </c>
       <c r="D98" s="7" t="inlineStr">
         <is>
-          <t>학교폭력</t>
+          <t>안전</t>
         </is>
       </c>
       <c r="E98" s="12" t="inlineStr">
         <is>
-          <t>https://www.easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=1408&amp;ccfNo=1&amp;cciNo=1&amp;cnpClsNo=1</t>
+          <t>https://www.easylaw.go.kr/CSP/CnpClsMainBtr.laf?popMenu=ov&amp;csmSeq=690&amp;ccfNo=1&amp;cciNo=3&amp;cnpClsNo=1</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="14" t="inlineStr">
         <is>
-          <t>행정안전부</t>
+          <t>법제처(찾기쉬운 생활법령정보)</t>
         </is>
       </c>
       <c r="B99" s="14" t="inlineStr">
         <is>
-          <t>어린이 안전 배움터 - 자전거 안전(놀이기구)</t>
+          <t>학교폭력 &gt; 학교폭력의 이해 &gt; 학교폭력의 개념 (학교폭력예방 및 대책에 관한 법률 제2조)</t>
         </is>
       </c>
       <c r="C99" s="13" t="n">
@@ -30346,10 +30346,35 @@
       </c>
       <c r="D99" s="14" t="inlineStr">
         <is>
+          <t>학교폭력</t>
+        </is>
+      </c>
+      <c r="E99" s="15" t="inlineStr">
+        <is>
+          <t>https://www.easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=1408&amp;ccfNo=1&amp;cciNo=1&amp;cnpClsNo=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="7" t="inlineStr">
+        <is>
+          <t>행정안전부</t>
+        </is>
+      </c>
+      <c r="B100" s="7" t="inlineStr">
+        <is>
+          <t>어린이 안전 배움터 - 자전거 안전(놀이기구)</t>
+        </is>
+      </c>
+      <c r="C100" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D100" s="7" t="inlineStr">
+        <is>
           <t>안전</t>
         </is>
       </c>
-      <c r="E99" s="15" t="inlineStr">
+      <c r="E100" s="12" t="inlineStr">
         <is>
           <t>https://www.mois.go.kr/chd/sub/a06/play/screen.do</t>
         </is>
@@ -30431,6 +30456,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E97" r:id="rId72"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E98" r:id="rId73"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E99" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E100" r:id="rId75"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
